--- a/ボランティアカフェ_開催準備リスト_20261215.xlsx
+++ b/ボランティアカフェ_開催準備リスト_20261215.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="使い方" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="当日の流れ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="準備リスト" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="逆算スケジュール" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="予算50,000円" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="グラフ" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当日の流れ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="準備リスト" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="逆算スケジュール" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="予算50,000円" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="グラフ" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'当日の流れ'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'準備リスト'!$A$4:$K$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'準備リスト'!$A$4:$K$119</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'準備リスト'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'逆算スケジュール'!$4:$4</definedName>
   </definedNames>
@@ -588,13 +588,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -618,10 +618,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2E7D5B"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -646,10 +646,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="C3D3C6"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -691,8 +691,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -718,13 +718,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -748,22 +748,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2E7D5B"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'グラフ'!$F$5:$F$14</f>
+              <f>'グラフ'!$F$5:$F$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'グラフ'!$G$5:$G$14</f>
+              <f>'グラフ'!$G$5:$G$15</f>
             </numRef>
           </val>
         </ser>
@@ -776,22 +776,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="C3D3C6"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'グラフ'!$F$5:$F$14</f>
+              <f>'グラフ'!$F$5:$F$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'グラフ'!$H$5:$H$14</f>
+              <f>'グラフ'!$H$5:$H$15</f>
             </numRef>
           </val>
         </ser>
@@ -809,8 +809,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -864,7 +864,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -879,9 +879,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -901,9 +901,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1331,7 +1331,7 @@
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>・「準備リスト」… やることを103項目、締切の早い順にならべています。</t>
+          <t>・「準備リスト」… やることを115項目、締切の早い順にならべています。</t>
         </is>
       </c>
       <c r="B14" s="11" t="n"/>
@@ -2126,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3011,7 +3011,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="33">
-        <f>使い方!$B$5-35</f>
+        <f>使い方!$B$5-42</f>
         <v/>
       </c>
       <c r="C22" s="34">
@@ -3020,22 +3020,22 @@
       </c>
       <c r="D22" s="35" t="inlineStr">
         <is>
-          <t>5週前</t>
+          <t>6週前</t>
         </is>
       </c>
       <c r="E22" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>既存の資料一式を出して、そろっているか確認する</t>
+          <t>町の備蓄にある段ボールベッドの台数を確認し、借用を依頼する</t>
         </is>
       </c>
       <c r="G22" s="26" t="inlineStr">
         <is>
-          <t>福祉教育プログラム「災害ボランティアセンター運営体験」の様式・進行表</t>
+          <t>何台借りられるか、受け取りと返却の方法をあわせて確認する。借用が基本、足りない分だけ購入する</t>
         </is>
       </c>
       <c r="H22" s="27" t="n"/>
@@ -3045,14 +3045,18 @@
         </is>
       </c>
       <c r="J22" s="36" t="n"/>
-      <c r="K22" s="37" t="n"/>
+      <c r="K22" s="37" t="inlineStr">
+        <is>
+          <t>11月3日は文化の日。前後にずらす</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="32" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="33">
-        <f>使い方!$B$5-35</f>
+        <f>使い方!$B$5-42</f>
         <v/>
       </c>
       <c r="C23" s="34">
@@ -3061,22 +3065,22 @@
       </c>
       <c r="D23" s="35" t="inlineStr">
         <is>
-          <t>5週前</t>
+          <t>6週前</t>
         </is>
       </c>
       <c r="E23" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F23" s="10" t="inlineStr">
         <is>
-          <t>縮小版の構成を決める</t>
+          <t>当日使う段ボールベッドの台数を決める</t>
         </is>
       </c>
       <c r="G23" s="26" t="inlineStr">
         <is>
-          <t>受付 → ニーズ受付 → マッチング → 送り出し の4場面を、20〜30分で通す。説明は短く、動かす時間を長く</t>
+          <t>1台を4〜5人で組むのがめやす。定員50人なら体験用に数台。組み立て済みを1台置いておくと、完成形が分かります</t>
         </is>
       </c>
       <c r="H23" s="27" t="n"/>
@@ -3086,14 +3090,18 @@
         </is>
       </c>
       <c r="J23" s="36" t="n"/>
-      <c r="K23" s="37" t="n"/>
+      <c r="K23" s="37" t="inlineStr">
+        <is>
+          <t>11月3日は文化の日。前後にずらす</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="32" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="33">
-        <f>使い方!$B$5-35</f>
+        <f>使い方!$B$5-42</f>
         <v/>
       </c>
       <c r="C24" s="34">
@@ -3102,22 +3110,22 @@
       </c>
       <c r="D24" s="35" t="inlineStr">
         <is>
-          <t>5週前</t>
+          <t>6週前</t>
         </is>
       </c>
       <c r="E24" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>講座（10:00〜11:00）の構成を決める</t>
+          <t>展示する最新の防災グッズを選び、購入リストをつくる</t>
         </is>
       </c>
       <c r="G24" s="26" t="inlineStr">
         <is>
-          <t>前半「ボランティアとは」＋後半「災害ボランティアセンターの運営」。60分をどう割るかを先に決める</t>
+          <t>予算内で。「見たことがない」「さわってみたい」と思えるものを優先する。予算シートは10,000円で計上</t>
         </is>
       </c>
       <c r="H24" s="27" t="n"/>
@@ -3127,14 +3135,18 @@
         </is>
       </c>
       <c r="J24" s="36" t="n"/>
-      <c r="K24" s="37" t="n"/>
+      <c r="K24" s="37" t="inlineStr">
+        <is>
+          <t>11月3日は文化の日。前後にずらす</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="32" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="33">
-        <f>使い方!$B$5-35</f>
+        <f>使い方!$B$5-42</f>
         <v/>
       </c>
       <c r="C25" s="34">
@@ -3143,22 +3155,22 @@
       </c>
       <c r="D25" s="35" t="inlineStr">
         <is>
-          <t>5週前</t>
+          <t>6週前</t>
         </is>
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F25" s="10" t="inlineStr">
         <is>
-          <t>講座で話す人を決める</t>
+          <t>役場総務課防災対策室へ、防災バッグの借用を依頼する</t>
         </is>
       </c>
       <c r="G25" s="26" t="inlineStr">
         <is>
-          <t>職員が話すか、外部にお願いするか。外部なら謝礼と依頼文が要ります</t>
+          <t>中身を見せる展示に使います。受け取りと返却の方法、中身を出して並べてよいかもあわせて確認する</t>
         </is>
       </c>
       <c r="H25" s="27" t="n"/>
@@ -3168,7 +3180,11 @@
         </is>
       </c>
       <c r="J25" s="36" t="n"/>
-      <c r="K25" s="37" t="n"/>
+      <c r="K25" s="37" t="inlineStr">
+        <is>
+          <t>11月3日は文化の日。前後にずらす</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="32" t="n">
@@ -3194,12 +3210,12 @@
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>大郷町の防災士のうち、誰に応援をお願いするか決める</t>
+          <t>既存の資料一式を出して、そろっているか確認する</t>
         </is>
       </c>
       <c r="G26" s="26" t="inlineStr">
         <is>
-          <t>町の防災担当課と相談して名簿を確認する。連絡先は持ち出さず、依頼は社協から出す</t>
+          <t>福祉教育プログラム「災害ボランティアセンター運営体験」の様式・進行表</t>
         </is>
       </c>
       <c r="H26" s="27" t="n"/>
@@ -3235,12 +3251,12 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>防災士へ出す応援依頼文をつくる</t>
+          <t>縮小版の構成を決める</t>
         </is>
       </c>
       <c r="G27" s="26" t="inlineStr">
         <is>
-          <t>1枚に：依頼の趣旨（災害ボランティアセンター運営体験の手伝い）／日時・会場／お願いしたい役割／返事の期限（4週前まで）／社協の連絡先</t>
+          <t>受付 → ニーズ受付 → マッチング → 送り出し の4場面を、20〜30分で通す。説明は短く、動かす時間を長く</t>
         </is>
       </c>
       <c r="H27" s="27" t="n"/>
@@ -3257,7 +3273,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="33">
-        <f>使い方!$B$5-28</f>
+        <f>使い方!$B$5-35</f>
         <v/>
       </c>
       <c r="C28" s="34">
@@ -3266,22 +3282,22 @@
       </c>
       <c r="D28" s="35" t="inlineStr">
         <is>
-          <t>4週前</t>
+          <t>5週前</t>
         </is>
       </c>
       <c r="E28" s="26" t="inlineStr">
         <is>
-          <t>A 会場をおさえる</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>設備を確認する</t>
+          <t>講座（10:00〜11:00）の構成を決める</t>
         </is>
       </c>
       <c r="G28" s="26" t="inlineStr">
         <is>
-          <t>電源の位置と数／暖房／給湯室／机といすの数／ゴミは持ち帰りか／掲示物を壁に貼ってよいか</t>
+          <t>前半「ボランティアとは」＋後半「災害ボランティアセンターの運営」。60分をどう割るかを先に決める</t>
         </is>
       </c>
       <c r="H28" s="27" t="n"/>
@@ -3298,7 +3314,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="33">
-        <f>使い方!$B$5-28</f>
+        <f>使い方!$B$5-35</f>
         <v/>
       </c>
       <c r="C29" s="34">
@@ -3307,22 +3323,22 @@
       </c>
       <c r="D29" s="35" t="inlineStr">
         <is>
-          <t>4週前</t>
+          <t>5週前</t>
         </is>
       </c>
       <c r="E29" s="26" t="inlineStr">
         <is>
-          <t>A 会場をおさえる</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>前日12月14日（月）15:00から会場に入れるか確認する</t>
+          <t>講座で話す人を決める</t>
         </is>
       </c>
       <c r="G29" s="26" t="inlineStr">
         <is>
-          <t>粕川地区防災コミュニティセンター。前日準備の時間帯に使用申請が要るかも確認</t>
+          <t>職員が話すか、外部にお願いするか。外部なら謝礼と依頼文が要ります</t>
         </is>
       </c>
       <c r="H29" s="27" t="n"/>
@@ -3332,18 +3348,14 @@
         </is>
       </c>
       <c r="J29" s="36" t="n"/>
-      <c r="K29" s="37" t="inlineStr">
-        <is>
-          <t>会場は粕川地区防災コミュニティセンターに決定済み</t>
-        </is>
-      </c>
+      <c r="K29" s="37" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="32" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="33">
-        <f>使い方!$B$5-28</f>
+        <f>使い方!$B$5-35</f>
         <v/>
       </c>
       <c r="C30" s="34">
@@ -3352,22 +3364,22 @@
       </c>
       <c r="D30" s="35" t="inlineStr">
         <is>
-          <t>4週前</t>
+          <t>5週前</t>
         </is>
       </c>
       <c r="E30" s="26" t="inlineStr">
         <is>
-          <t>B 事務の手続き</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>ボランティア活動保険の加入状況を確認する</t>
+          <t>大郷町の防災士のうち、誰に応援をお願いするか決める</t>
         </is>
       </c>
       <c r="G30" s="26" t="inlineStr">
         <is>
-          <t>盆栽の道具（はさみ）と災ボラ体験の資機材を扱います。参加者に保険が要るかを整理し、必要なら加入用紙を用意</t>
+          <t>町の防災担当課と相談して名簿を確認する。連絡先は持ち出さず、依頼は社協から出す</t>
         </is>
       </c>
       <c r="H30" s="27" t="n"/>
@@ -3384,7 +3396,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="33">
-        <f>使い方!$B$5-28</f>
+        <f>使い方!$B$5-35</f>
         <v/>
       </c>
       <c r="C31" s="34">
@@ -3393,22 +3405,22 @@
       </c>
       <c r="D31" s="35" t="inlineStr">
         <is>
-          <t>4週前</t>
+          <t>5週前</t>
         </is>
       </c>
       <c r="E31" s="26" t="inlineStr">
         <is>
-          <t>C チラシと広報</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>区長・行政区へ回覧を依頼する</t>
+          <t>防災士へ出す応援依頼文をつくる</t>
         </is>
       </c>
       <c r="G31" s="26" t="inlineStr">
         <is>
-          <t>回りきるまで2〜3週間かかります。開催3週前には回りはじめるよう逆算</t>
+          <t>1枚に：依頼の趣旨（災害ボランティアセンター運営体験の手伝い）／日時・会場／お願いしたい役割／返事の期限（4週前まで）／社協の連絡先</t>
         </is>
       </c>
       <c r="H31" s="27" t="n"/>
@@ -3425,7 +3437,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="33">
-        <f>使い方!$B$5-28</f>
+        <f>使い方!$B$5-35</f>
         <v/>
       </c>
       <c r="C32" s="34">
@@ -3434,22 +3446,22 @@
       </c>
       <c r="D32" s="35" t="inlineStr">
         <is>
-          <t>4週前</t>
+          <t>5週前</t>
         </is>
       </c>
       <c r="E32" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>飲みもの</t>
+          <t>借りられない不足分の段ボールベッドを購入する</t>
         </is>
       </c>
       <c r="G32" s="26" t="inlineStr">
         <is>
-          <t>お茶（温・冷）／コーヒー／紅茶／砂糖・ミルク／麦茶。夏冬で入れ替える</t>
+          <t>納期に注意。1台あたり約3,000円。購入するなら、その分どこかを削る必要があります（予算シート参照）</t>
         </is>
       </c>
       <c r="H32" s="27" t="n"/>
@@ -3466,7 +3478,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="33">
-        <f>使い方!$B$5-28</f>
+        <f>使い方!$B$5-35</f>
         <v/>
       </c>
       <c r="C33" s="34">
@@ -3475,20 +3487,24 @@
       </c>
       <c r="D33" s="35" t="inlineStr">
         <is>
-          <t>4週前</t>
+          <t>5週前</t>
         </is>
       </c>
       <c r="E33" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F33" s="10" t="inlineStr">
         <is>
-          <t>紙コップ・紙皿・おしぼり・つまようじ・ゴミ袋（分別の数だけ）</t>
-        </is>
-      </c>
-      <c r="G33" s="26" t="n"/>
+          <t>防災グッズを発注・購入する</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>納期に注意。届いたら箱から出して、当日すぐさわれる状態にしておく</t>
+        </is>
+      </c>
       <c r="H33" s="27" t="n"/>
       <c r="I33" s="27" t="inlineStr">
         <is>
@@ -3503,7 +3519,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="33">
-        <f>使い方!$B$5-28</f>
+        <f>使い方!$B$5-35</f>
         <v/>
       </c>
       <c r="C34" s="34">
@@ -3512,22 +3528,22 @@
       </c>
       <c r="D34" s="35" t="inlineStr">
         <is>
-          <t>4週前</t>
+          <t>5週前</t>
         </is>
       </c>
       <c r="E34" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>保温ポット2本、やかん、給湯の段取り</t>
+          <t>配食ボランティアのみなさんへ、当日の紹介コーナーへの協力をお願いする</t>
         </is>
       </c>
       <c r="G34" s="26" t="inlineStr">
         <is>
-          <t>会場で沸かせるか、社協から運ぶかを決めておく</t>
+          <t>写真をお借りするだけでも構いません。当日コーナーに立ってもらえるかも確認する</t>
         </is>
       </c>
       <c r="H34" s="27" t="n"/>
@@ -3558,17 +3574,17 @@
       </c>
       <c r="E35" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>A 会場をおさえる</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>名札（貼るタイプ）とケース、太めのサインペン</t>
+          <t>設備を確認する</t>
         </is>
       </c>
       <c r="G35" s="26" t="inlineStr">
         <is>
-          <t>呼ばれたい名前を大きく書いてもらいます。細いペンは使わない</t>
+          <t>電源の位置と数／暖房／給湯室／机といすの数／ゴミは持ち帰りか／掲示物を壁に貼ってよいか</t>
         </is>
       </c>
       <c r="H35" s="27" t="n"/>
@@ -3599,17 +3615,17 @@
       </c>
       <c r="E36" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>A 会場をおさえる</t>
         </is>
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>自由見学（11:00〜12:00）のコーナー構成を決める</t>
+          <t>前日12月14日（月）15:00から会場に入れるか確認する</t>
         </is>
       </c>
       <c r="G36" s="26" t="inlineStr">
         <is>
-          <t>案：災ボラの資機材展示／マッチング体験／町の活動紹介パネル／盆栽コーナー／お茶と相談。何を何か所置くかを先に決める</t>
+          <t>粕川地区防災コミュニティセンター。前日準備の時間帯に使用申請が要るかも確認</t>
         </is>
       </c>
       <c r="H36" s="27" t="n"/>
@@ -3619,7 +3635,11 @@
         </is>
       </c>
       <c r="J36" s="36" t="n"/>
-      <c r="K36" s="37" t="n"/>
+      <c r="K36" s="37" t="inlineStr">
+        <is>
+          <t>会場は粕川地区防災コミュニティセンターに決定済み</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="32" t="n">
@@ -3640,17 +3660,17 @@
       </c>
       <c r="E37" s="26" t="inlineStr">
         <is>
-          <t>G 盆栽ボランティアの準備</t>
+          <t>B 事務の手続き</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>材料を発注する</t>
+          <t>ボランティア活動保険の加入状況を確認する</t>
         </is>
       </c>
       <c r="G37" s="26" t="inlineStr">
         <is>
-          <t>苗木／鉢／用土／鉢底ネット／鉢底石／化粧砂／ラベル</t>
+          <t>盆栽の道具（はさみ）と災ボラ体験の資機材を扱います。参加者に保険が要るかを整理し、必要なら加入用紙を用意</t>
         </is>
       </c>
       <c r="H37" s="27" t="n"/>
@@ -3681,17 +3701,17 @@
       </c>
       <c r="E38" s="26" t="inlineStr">
         <is>
-          <t>G 盆栽ボランティアの準備</t>
+          <t>C チラシと広報</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>道具をそろえる</t>
+          <t>区長・行政区へ回覧を依頼する</t>
         </is>
       </c>
       <c r="G38" s="26" t="inlineStr">
         <is>
-          <t>剪定ばさみ（人数分は要りません。3〜4本を回す）／ピンセット／じょうろ／園芸用の針金／割り箸／土入れ</t>
+          <t>回りきるまで2〜3週間かかります。開催3週前には回りはじめるよう逆算</t>
         </is>
       </c>
       <c r="H38" s="27" t="n"/>
@@ -3722,15 +3742,19 @@
       </c>
       <c r="E39" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>ボランティア受付票を必要部数印刷する</t>
-        </is>
-      </c>
-      <c r="G39" s="26" t="n"/>
+          <t>飲みもの</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>お茶（温・冷）／コーヒー／紅茶／砂糖・ミルク／麦茶。夏冬で入れ替える</t>
+        </is>
+      </c>
       <c r="H39" s="27" t="n"/>
       <c r="I39" s="27" t="inlineStr">
         <is>
@@ -3759,19 +3783,15 @@
       </c>
       <c r="E40" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>ニーズ受付票を印刷し、想定の事例を5〜8件つくる</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="inlineStr">
-        <is>
-          <t>大郷町で実際に起こりうる困りごとで。「二階まで水が来た」「ひとり暮らしで家財が出せない」など、地名を入れると急に自分ごとになります</t>
-        </is>
-      </c>
+          <t>紙コップ・紙皿・おしぼり・つまようじ・ゴミ袋（分別の数だけ）</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="n"/>
       <c r="H40" s="27" t="n"/>
       <c r="I40" s="27" t="inlineStr">
         <is>
@@ -3800,17 +3820,17 @@
       </c>
       <c r="E41" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>防災士へ依頼文を出し、来てくれる人と当日の役割を決める</t>
+          <t>保温ポット2本、やかん、給湯の段取り</t>
         </is>
       </c>
       <c r="G41" s="26" t="inlineStr">
         <is>
-          <t>役割の案：資機材の説明、マッチング体験の進行、受付の補助。何人来られるかで自由見学のコーナー数が決まります</t>
+          <t>会場で沸かせるか、社協から運ぶかを決めておく</t>
         </is>
       </c>
       <c r="H41" s="27" t="n"/>
@@ -3820,18 +3840,14 @@
         </is>
       </c>
       <c r="J41" s="36" t="n"/>
-      <c r="K41" s="37" t="inlineStr">
-        <is>
-          <t>4週前（11/17）までに人数を確定する</t>
-        </is>
-      </c>
+      <c r="K41" s="37" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="32" t="n">
         <v>38</v>
       </c>
       <c r="B42" s="33">
-        <f>使い方!$B$5-21</f>
+        <f>使い方!$B$5-28</f>
         <v/>
       </c>
       <c r="C42" s="34">
@@ -3840,22 +3856,22 @@
       </c>
       <c r="D42" s="35" t="inlineStr">
         <is>
-          <t>3週前</t>
+          <t>4週前</t>
         </is>
       </c>
       <c r="E42" s="26" t="inlineStr">
         <is>
-          <t>A 会場をおさえる</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>当日は9:00開場のため、8:30に鍵を開けられるか確認する</t>
+          <t>名札（貼るタイプ）とケース、太めのサインペン</t>
         </is>
       </c>
       <c r="G42" s="26" t="inlineStr">
         <is>
-          <t>職員集合は8:30。鍵の受け取り方と、当日の連絡先もあわせて</t>
+          <t>呼ばれたい名前を大きく書いてもらいます。細いペンは使わない</t>
         </is>
       </c>
       <c r="H42" s="27" t="n"/>
@@ -3872,7 +3888,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="33">
-        <f>使い方!$B$5-21</f>
+        <f>使い方!$B$5-28</f>
         <v/>
       </c>
       <c r="C43" s="34">
@@ -3881,22 +3897,22 @@
       </c>
       <c r="D43" s="35" t="inlineStr">
         <is>
-          <t>3週前</t>
+          <t>4週前</t>
         </is>
       </c>
       <c r="E43" s="26" t="inlineStr">
         <is>
-          <t>B 事務の手続き</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>個人情報の扱いを決める</t>
+          <t>自由見学（11:00〜12:00）のコーナー構成を決める</t>
         </is>
       </c>
       <c r="G43" s="26" t="inlineStr">
         <is>
-          <t>参加者カードの保管場所・保管期間・持ち出しの可否。世話人・協力者にも書面で説明</t>
+          <t>案：災ボラの資機材展示／マッチング体験／町の活動紹介パネル／盆栽コーナー／お茶と相談。何を何か所置くかを先に決める</t>
         </is>
       </c>
       <c r="H43" s="27" t="n"/>
@@ -3913,7 +3929,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="33">
-        <f>使い方!$B$5-21</f>
+        <f>使い方!$B$5-28</f>
         <v/>
       </c>
       <c r="C44" s="34">
@@ -3922,22 +3938,22 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>3週前</t>
+          <t>4週前</t>
         </is>
       </c>
       <c r="E44" s="26" t="inlineStr">
         <is>
-          <t>B 事務の手続き</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>写真撮影の同意の取り方を決める</t>
+          <t>材料を発注する</t>
         </is>
       </c>
       <c r="G44" s="26" t="inlineStr">
         <is>
-          <t>受付での口頭確認と、会場の掲示。写りたくない方の名札に印をつける方法まで</t>
+          <t>苗木／鉢／用土／鉢底ネット／鉢底石／化粧砂／ラベル</t>
         </is>
       </c>
       <c r="H44" s="27" t="n"/>
@@ -3954,7 +3970,7 @@
         <v>41</v>
       </c>
       <c r="B45" s="33">
-        <f>使い方!$B$5-21</f>
+        <f>使い方!$B$5-28</f>
         <v/>
       </c>
       <c r="C45" s="34">
@@ -3963,22 +3979,22 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>3週前</t>
+          <t>4週前</t>
         </is>
       </c>
       <c r="E45" s="26" t="inlineStr">
         <is>
-          <t>C チラシと広報</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>掲示をお願いして回る</t>
+          <t>道具をそろえる</t>
         </is>
       </c>
       <c r="G45" s="26" t="inlineStr">
         <is>
-          <t>公民館／支所／診療所／商店／郵便局／スーパー／温泉施設／集会所</t>
+          <t>剪定ばさみ（人数分は要りません。3〜4本を回す）／ピンセット／じょうろ／園芸用の針金／割り箸／土入れ</t>
         </is>
       </c>
       <c r="H45" s="27" t="n"/>
@@ -3995,7 +4011,7 @@
         <v>42</v>
       </c>
       <c r="B46" s="33">
-        <f>使い方!$B$5-21</f>
+        <f>使い方!$B$5-28</f>
         <v/>
       </c>
       <c r="C46" s="34">
@@ -4004,24 +4020,20 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>3週前</t>
+          <t>4週前</t>
         </is>
       </c>
       <c r="E46" s="26" t="inlineStr">
         <is>
-          <t>C チラシと広報</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>直接声をかける（まず20人）</t>
-        </is>
-      </c>
-      <c r="G46" s="26" t="inlineStr">
-        <is>
-          <t>ボランティア入門講座の修了者／サロン参加者／登録ボランティア。名簿を見ながら、電話か手渡しで</t>
-        </is>
-      </c>
+          <t>ボランティア受付票を必要部数印刷する</t>
+        </is>
+      </c>
+      <c r="G46" s="26" t="n"/>
       <c r="H46" s="27" t="n"/>
       <c r="I46" s="27" t="inlineStr">
         <is>
@@ -4036,7 +4048,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="33">
-        <f>使い方!$B$5-21</f>
+        <f>使い方!$B$5-28</f>
         <v/>
       </c>
       <c r="C47" s="34">
@@ -4045,22 +4057,22 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>3週前</t>
+          <t>4週前</t>
         </is>
       </c>
       <c r="E47" s="26" t="inlineStr">
         <is>
-          <t>C チラシと広報</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F47" s="10" t="inlineStr">
         <is>
-          <t>民生委員児童委員・地区社協・地域包括支援センターへ情報提供</t>
+          <t>ニーズ受付票を印刷し、想定の事例を5〜8件つくる</t>
         </is>
       </c>
       <c r="G47" s="26" t="inlineStr">
         <is>
-          <t>気になっている方に声をかけてもらう。「誘ってあげてください」と具体的に頼む</t>
+          <t>大郷町で実際に起こりうる困りごとで。「二階まで水が来た」「ひとり暮らしで家財が出せない」など、地名を入れると急に自分ごとになります</t>
         </is>
       </c>
       <c r="H47" s="27" t="n"/>
@@ -4077,7 +4089,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="33">
-        <f>使い方!$B$5-21</f>
+        <f>使い方!$B$5-28</f>
         <v/>
       </c>
       <c r="C48" s="34">
@@ -4086,20 +4098,24 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>3週前</t>
+          <t>4週前</t>
         </is>
       </c>
       <c r="E48" s="26" t="inlineStr">
         <is>
-          <t>C チラシと広報</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>ホームページ・SNSに掲載する</t>
-        </is>
-      </c>
-      <c r="G48" s="26" t="n"/>
+          <t>防災士へ依頼文を出し、来てくれる人と当日の役割を決める</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t>役割の案：資機材の説明、マッチング体験の進行、受付の補助。何人来られるかで自由見学のコーナー数が決まります</t>
+        </is>
+      </c>
       <c r="H48" s="27" t="n"/>
       <c r="I48" s="27" t="inlineStr">
         <is>
@@ -4107,7 +4123,11 @@
         </is>
       </c>
       <c r="J48" s="36" t="n"/>
-      <c r="K48" s="37" t="n"/>
+      <c r="K48" s="37" t="inlineStr">
+        <is>
+          <t>4週前（11/17）までに人数を確定する</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="32" t="n">
@@ -4128,15 +4148,19 @@
       </c>
       <c r="E49" s="26" t="inlineStr">
         <is>
-          <t>D 参加記念品</t>
+          <t>A 会場をおさえる</t>
         </is>
       </c>
       <c r="F49" s="10" t="inlineStr">
         <is>
-          <t>納品を確認し、数を数える</t>
-        </is>
-      </c>
-      <c r="G49" s="26" t="n"/>
+          <t>当日は9:00開場のため、8:30に鍵を開けられるか確認する</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>職員集合は8:30。鍵の受け取り方と、当日の連絡先もあわせて</t>
+        </is>
+      </c>
       <c r="H49" s="27" t="n"/>
       <c r="I49" s="27" t="inlineStr">
         <is>
@@ -4165,17 +4189,17 @@
       </c>
       <c r="E50" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>B 事務の手続き</t>
         </is>
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>建物の入口から会場までの順路表示（矢印を3枚以上）</t>
+          <t>個人情報の扱いを決める</t>
         </is>
       </c>
       <c r="G50" s="26" t="inlineStr">
         <is>
-          <t>はじめての方は、入口で引き返します。外の道路からの1枚目がいちばん大事</t>
+          <t>参加者カードの保管場所・保管期間・持ち出しの可否。世話人・協力者にも書面で説明</t>
         </is>
       </c>
       <c r="H50" s="27" t="n"/>
@@ -4206,15 +4230,19 @@
       </c>
       <c r="E51" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>B 事務の手続き</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>受付の看板「ボランティアカフェ 受付」</t>
-        </is>
-      </c>
-      <c r="G51" s="26" t="n"/>
+          <t>写真撮影の同意の取り方を決める</t>
+        </is>
+      </c>
+      <c r="G51" s="26" t="inlineStr">
+        <is>
+          <t>受付での口頭確認と、会場の掲示。写りたくない方の名札に印をつける方法まで</t>
+        </is>
+      </c>
       <c r="H51" s="27" t="n"/>
       <c r="I51" s="27" t="inlineStr">
         <is>
@@ -4243,17 +4271,17 @@
       </c>
       <c r="E52" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>C チラシと広報</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>本日の流れ（90分の進行を大きく1枚）</t>
+          <t>掲示をお願いして回る</t>
         </is>
       </c>
       <c r="G52" s="26" t="inlineStr">
         <is>
-          <t>途中から来た方が、見れば分かるように</t>
+          <t>公民館／支所／診療所／商店／郵便局／スーパー／温泉施設／集会所</t>
         </is>
       </c>
       <c r="H52" s="27" t="n"/>
@@ -4284,15 +4312,19 @@
       </c>
       <c r="E53" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>C チラシと広報</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>テーブル番号（1〜4）</t>
-        </is>
-      </c>
-      <c r="G53" s="26" t="n"/>
+          <t>直接声をかける（まず20人）</t>
+        </is>
+      </c>
+      <c r="G53" s="26" t="inlineStr">
+        <is>
+          <t>ボランティア入門講座の修了者／サロン参加者／登録ボランティア。名簿を見ながら、電話か手渡しで</t>
+        </is>
+      </c>
       <c r="H53" s="27" t="n"/>
       <c r="I53" s="27" t="inlineStr">
         <is>
@@ -4321,15 +4353,19 @@
       </c>
       <c r="E54" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>C チラシと広報</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>「写真を撮ります。写りたくない方は受付でお申し出ください」の掲示</t>
-        </is>
-      </c>
-      <c r="G54" s="26" t="n"/>
+          <t>民生委員児童委員・地区社協・地域包括支援センターへ情報提供</t>
+        </is>
+      </c>
+      <c r="G54" s="26" t="inlineStr">
+        <is>
+          <t>気になっている方に声をかけてもらう。「誘ってあげてください」と具体的に頼む</t>
+        </is>
+      </c>
       <c r="H54" s="27" t="n"/>
       <c r="I54" s="27" t="inlineStr">
         <is>
@@ -4358,19 +4394,15 @@
       </c>
       <c r="E55" s="26" t="inlineStr">
         <is>
-          <t>G 盆栽ボランティアの準備</t>
+          <t>C チラシと広報</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>汚れ対策をそろえる</t>
-        </is>
-      </c>
-      <c r="G55" s="26" t="inlineStr">
-        <is>
-          <t>ブルーシート／新聞紙／テーブルに敷くもの／雑巾／バケツ／ほうきとちりとり</t>
-        </is>
-      </c>
+          <t>ホームページ・SNSに掲載する</t>
+        </is>
+      </c>
+      <c r="G55" s="26" t="n"/>
       <c r="H55" s="27" t="n"/>
       <c r="I55" s="27" t="inlineStr">
         <is>
@@ -4399,19 +4431,15 @@
       </c>
       <c r="E56" s="26" t="inlineStr">
         <is>
-          <t>G 盆栽ボランティアの準備</t>
+          <t>D 参加記念品</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>軍手（人数分＋予備5）</t>
-        </is>
-      </c>
-      <c r="G56" s="26" t="inlineStr">
-        <is>
-          <t>手の汚れを気にして参加をやめる方がいます。軍手は必ず余分に</t>
-        </is>
-      </c>
+          <t>納品を確認し、数を数える</t>
+        </is>
+      </c>
+      <c r="G56" s="26" t="n"/>
       <c r="H56" s="27" t="n"/>
       <c r="I56" s="27" t="inlineStr">
         <is>
@@ -4440,17 +4468,17 @@
       </c>
       <c r="E57" s="26" t="inlineStr">
         <is>
-          <t>G 盆栽ボランティアの準備</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>手洗い場所と、そこまでの動線を決める</t>
+          <t>建物の入口から会場までの順路表示（矢印を3枚以上）</t>
         </is>
       </c>
       <c r="G57" s="26" t="inlineStr">
         <is>
-          <t>土のついた手で歩く道すじに、新聞紙を敷いておく</t>
+          <t>はじめての方は、入口で引き返します。外の道路からの1枚目がいちばん大事</t>
         </is>
       </c>
       <c r="H57" s="27" t="n"/>
@@ -4481,19 +4509,15 @@
       </c>
       <c r="E58" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>マッチング用のボードをつくる</t>
-        </is>
-      </c>
-      <c r="G58" s="26" t="inlineStr">
-        <is>
-          <t>模造紙とカード、マグネットかマスキングテープ。人数と作業内容を貼り合わせる形に</t>
-        </is>
-      </c>
+          <t>受付の看板「ボランティアカフェ 受付」</t>
+        </is>
+      </c>
+      <c r="G58" s="26" t="n"/>
       <c r="H58" s="27" t="n"/>
       <c r="I58" s="27" t="inlineStr">
         <is>
@@ -4522,17 +4546,17 @@
       </c>
       <c r="E59" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F59" s="10" t="inlineStr">
         <is>
-          <t>役割の名札をつくる</t>
+          <t>本日の流れ（90分の進行を大きく1枚）</t>
         </is>
       </c>
       <c r="G59" s="26" t="inlineStr">
         <is>
-          <t>受付／ニーズ／マッチング／資材／送り出し。首から下げる形にすると、役になりきれます</t>
+          <t>途中から来た方が、見れば分かるように</t>
         </is>
       </c>
       <c r="H59" s="27" t="n"/>
@@ -4563,19 +4587,15 @@
       </c>
       <c r="E60" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>資機材の見本を1つずつ用意する</t>
-        </is>
-      </c>
-      <c r="G60" s="26" t="inlineStr">
-        <is>
-          <t>スコップ／土のう袋／長靴／軍手／ヘルメット／一輪車。写真より、本物が1つあるほうが伝わります</t>
-        </is>
-      </c>
+          <t>テーブル番号（1〜4）</t>
+        </is>
+      </c>
+      <c r="G60" s="26" t="n"/>
       <c r="H60" s="27" t="n"/>
       <c r="I60" s="27" t="inlineStr">
         <is>
@@ -4604,19 +4624,15 @@
       </c>
       <c r="E61" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>説明用の掲示をつくる</t>
-        </is>
-      </c>
-      <c r="G61" s="26" t="inlineStr">
-        <is>
-          <t>「大郷町で災害が起きたら、災害ボランティアセンターはどこに、いつ立ち上がるか」を1枚に</t>
-        </is>
-      </c>
+          <t>「写真を撮ります。写りたくない方は受付でお申し出ください」の掲示</t>
+        </is>
+      </c>
+      <c r="G61" s="26" t="n"/>
       <c r="H61" s="27" t="n"/>
       <c r="I61" s="27" t="inlineStr">
         <is>
@@ -4645,15 +4661,19 @@
       </c>
       <c r="E62" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>ボランティア活動保険の説明資料と加入用紙を用意する</t>
-        </is>
-      </c>
-      <c r="G62" s="26" t="n"/>
+          <t>汚れ対策をそろえる</t>
+        </is>
+      </c>
+      <c r="G62" s="26" t="inlineStr">
+        <is>
+          <t>ブルーシート／新聞紙／テーブルに敷くもの／雑巾／バケツ／ほうきとちりとり</t>
+        </is>
+      </c>
       <c r="H62" s="27" t="n"/>
       <c r="I62" s="27" t="inlineStr">
         <is>
@@ -4682,17 +4702,17 @@
       </c>
       <c r="E63" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F63" s="10" t="inlineStr">
         <is>
-          <t>講座の資料・スライドをつくる</t>
+          <t>軍手（人数分＋予備5）</t>
         </is>
       </c>
       <c r="G63" s="26" t="inlineStr">
         <is>
-          <t>配布資料は文字を大きく。60分は長いので、途中に手を動かす時間か問いかけを入れる</t>
+          <t>手の汚れを気にして参加をやめる方がいます。軍手は必ず余分に</t>
         </is>
       </c>
       <c r="H63" s="27" t="n"/>
@@ -4709,7 +4729,7 @@
         <v>60</v>
       </c>
       <c r="B64" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C64" s="34">
@@ -4718,22 +4738,22 @@
       </c>
       <c r="D64" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E64" s="26" t="inlineStr">
         <is>
-          <t>A 会場をおさえる</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
         <is>
-          <t>レイアウト図をつくる</t>
+          <t>手洗い場所と、そこまでの動線を決める</t>
         </is>
       </c>
       <c r="G64" s="26" t="inlineStr">
         <is>
-          <t>受付／テーブル4つ／盆栽コーナー／災ボラ体験コーナー／給湯・ゴミ／記念品の置き場</t>
+          <t>土のついた手で歩く道すじに、新聞紙を敷いておく</t>
         </is>
       </c>
       <c r="H64" s="27" t="n"/>
@@ -4750,7 +4770,7 @@
         <v>61</v>
       </c>
       <c r="B65" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C65" s="34">
@@ -4759,22 +4779,22 @@
       </c>
       <c r="D65" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E65" s="26" t="inlineStr">
         <is>
-          <t>B 事務の手続き</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>食物アレルギーの対応を決める</t>
+          <t>マッチング用のボードをつくる</t>
         </is>
       </c>
       <c r="G65" s="26" t="inlineStr">
         <is>
-          <t>お菓子は個包装で、表示のあるものを。空袋を当日まで残しておく</t>
+          <t>模造紙とカード、マグネットかマスキングテープ。人数と作業内容を貼り合わせる形に</t>
         </is>
       </c>
       <c r="H65" s="27" t="n"/>
@@ -4791,7 +4811,7 @@
         <v>62</v>
       </c>
       <c r="B66" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C66" s="34">
@@ -4800,22 +4820,22 @@
       </c>
       <c r="D66" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E66" s="26" t="inlineStr">
         <is>
-          <t>D 参加記念品</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>添えるカードをつくる</t>
+          <t>役割の名札をつくる</t>
         </is>
       </c>
       <c r="G66" s="26" t="inlineStr">
         <is>
-          <t>「次回は◯月◯日です」「お問い合わせはボランティアセンターへ」。次につながる一言を入れる</t>
+          <t>受付／ニーズ／マッチング／資材／送り出し。首から下げる形にすると、役になりきれます</t>
         </is>
       </c>
       <c r="H66" s="27" t="n"/>
@@ -4832,7 +4852,7 @@
         <v>63</v>
       </c>
       <c r="B67" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C67" s="34">
@@ -4841,22 +4861,22 @@
       </c>
       <c r="D67" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E67" s="26" t="inlineStr">
         <is>
-          <t>D 参加記念品</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>袋詰めをする</t>
+          <t>資機材の見本を1つずつ用意する</t>
         </is>
       </c>
       <c r="G67" s="26" t="inlineStr">
         <is>
-          <t>記念品＋カード＋次回チラシをセットに。当日あわてないよう、前もって</t>
+          <t>スコップ／土のう袋／長靴／軍手／ヘルメット／一輪車。写真より、本物が1つあるほうが伝わります</t>
         </is>
       </c>
       <c r="H67" s="27" t="n"/>
@@ -4873,7 +4893,7 @@
         <v>64</v>
       </c>
       <c r="B68" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C68" s="34">
@@ -4882,20 +4902,24 @@
       </c>
       <c r="D68" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E68" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>参加者カード、筆記用具、クリップボード、受付名簿</t>
-        </is>
-      </c>
-      <c r="G68" s="26" t="n"/>
+          <t>説明用の掲示をつくる</t>
+        </is>
+      </c>
+      <c r="G68" s="26" t="inlineStr">
+        <is>
+          <t>「大郷町で災害が起きたら、災害ボランティアセンターはどこに、いつ立ち上がるか」を1枚に</t>
+        </is>
+      </c>
       <c r="H68" s="27" t="n"/>
       <c r="I68" s="27" t="inlineStr">
         <is>
@@ -4910,7 +4934,7 @@
         <v>65</v>
       </c>
       <c r="B69" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C69" s="34">
@@ -4919,24 +4943,20 @@
       </c>
       <c r="D69" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E69" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
         <is>
-          <t>テーブルクロス、花か観葉植物（1テーブルに1つ）</t>
-        </is>
-      </c>
-      <c r="G69" s="26" t="inlineStr">
-        <is>
-          <t>「会議」ではなく「カフェ」に見せるための、いちばん安い方法です</t>
-        </is>
-      </c>
+          <t>ボランティア活動保険の説明資料と加入用紙を用意する</t>
+        </is>
+      </c>
+      <c r="G69" s="26" t="n"/>
       <c r="H69" s="27" t="n"/>
       <c r="I69" s="27" t="inlineStr">
         <is>
@@ -4951,7 +4971,7 @@
         <v>66</v>
       </c>
       <c r="B70" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C70" s="34">
@@ -4960,22 +4980,22 @@
       </c>
       <c r="D70" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E70" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>小さなスピーカー（BGM用・小音量）</t>
+          <t>講座の資料・スライドをつくる</t>
         </is>
       </c>
       <c r="G70" s="26" t="inlineStr">
         <is>
-          <t>沈黙が気にならなくなり、はじめての方が入りやすくなります</t>
+          <t>配布資料は文字を大きく。60分は長いので、途中に手を動かす時間か問いかけを入れる</t>
         </is>
       </c>
       <c r="H70" s="27" t="n"/>
@@ -4992,7 +5012,7 @@
         <v>67</v>
       </c>
       <c r="B71" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C71" s="34">
@@ -5001,22 +5021,22 @@
       </c>
       <c r="D71" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E71" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>救急箱、消毒、絆創膏、体温計、ティッシュ</t>
+          <t>段ボールベッドの受け取り・運搬・返却の段取りを決める</t>
         </is>
       </c>
       <c r="G71" s="26" t="inlineStr">
         <is>
-          <t>盆栽ではさみを使うため、絆創膏は多めに</t>
+          <t>前日12/14の準備に間に合うように。かさばるので、運ぶ車と置き場所を先に決めておく</t>
         </is>
       </c>
       <c r="H71" s="27" t="n"/>
@@ -5033,7 +5053,7 @@
         <v>68</v>
       </c>
       <c r="B72" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C72" s="34">
@@ -5042,20 +5062,24 @@
       </c>
       <c r="D72" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E72" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>カメラ（記録用）、予備の電池</t>
-        </is>
-      </c>
-      <c r="G72" s="26" t="n"/>
+          <t>段ボールベッドの組み立て手順を、大きく1枚に書き出す</t>
+        </is>
+      </c>
+      <c r="G72" s="26" t="inlineStr">
+        <is>
+          <t>写真かイラストで3〜4ステップ。コーナーに貼っておけば、職員がつきっきりにならずにすみます</t>
+        </is>
+      </c>
       <c r="H72" s="27" t="n"/>
       <c r="I72" s="27" t="inlineStr">
         <is>
@@ -5070,7 +5094,7 @@
         <v>69</v>
       </c>
       <c r="B73" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C73" s="34">
@@ -5079,20 +5103,24 @@
       </c>
       <c r="D73" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E73" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
         <is>
-          <t>マスキングテープ、養生テープ、模造紙、はさみ、油性ペン</t>
-        </is>
-      </c>
-      <c r="G73" s="26" t="n"/>
+          <t>防災グッズと防災バッグの並べ方を決め、説明札をつくる</t>
+        </is>
+      </c>
+      <c r="G73" s="26" t="inlineStr">
+        <is>
+          <t>バッグの中身は出して並べる。一つずつに「なぜ要るか」を一言そえると、見るだけで学びになります</t>
+        </is>
+      </c>
       <c r="H73" s="27" t="n"/>
       <c r="I73" s="27" t="inlineStr">
         <is>
@@ -5107,7 +5135,7 @@
         <v>70</v>
       </c>
       <c r="B74" s="33">
-        <f>使い方!$B$5-14</f>
+        <f>使い方!$B$5-21</f>
         <v/>
       </c>
       <c r="C74" s="34">
@@ -5116,22 +5144,22 @@
       </c>
       <c r="D74" s="35" t="inlineStr">
         <is>
-          <t>2週前</t>
+          <t>3週前</t>
         </is>
       </c>
       <c r="E74" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>盆栽コーナーの表示と、手順の掲示</t>
+          <t>配食ボランティアの紹介パネル・写真を用意する</t>
         </is>
       </c>
       <c r="G74" s="26" t="inlineStr">
         <is>
-          <t>「土を入れる → 苗を置く → 水をやる」を、写真かイラストで3ステップに</t>
+          <t>活動のようすが分かる写真を数枚。町の活動紹介のコーナーにまとめて貼る</t>
         </is>
       </c>
       <c r="H74" s="27" t="n"/>
@@ -5162,17 +5190,17 @@
       </c>
       <c r="E75" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>A 会場をおさえる</t>
         </is>
       </c>
       <c r="F75" s="10" t="inlineStr">
         <is>
-          <t>災ボラ体験コーナーの表示（受付／ニーズ受付／マッチング／送り出しの4か所）</t>
+          <t>レイアウト図をつくる</t>
         </is>
       </c>
       <c r="G75" s="26" t="inlineStr">
         <is>
-          <t>本物の災害ボランティアセンターと同じ順に並べる。これ自体が説明になります</t>
+          <t>受付／テーブル4つ／盆栽コーナー／災ボラ体験コーナー／給湯・ゴミ／記念品の置き場</t>
         </is>
       </c>
       <c r="H75" s="27" t="n"/>
@@ -5203,17 +5231,17 @@
       </c>
       <c r="E76" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>B 事務の手続き</t>
         </is>
       </c>
       <c r="F76" s="10" t="inlineStr">
         <is>
-          <t>次回のご案内（日付を大きく1枚）</t>
+          <t>食物アレルギーの対応を決める</t>
         </is>
       </c>
       <c r="G76" s="26" t="inlineStr">
         <is>
-          <t>帰りぎわに必ず目に入る位置へ</t>
+          <t>お菓子は個包装で、表示のあるものを。空袋を当日まで残しておく</t>
         </is>
       </c>
       <c r="H76" s="27" t="n"/>
@@ -5244,17 +5272,17 @@
       </c>
       <c r="E77" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>D 参加記念品</t>
         </is>
       </c>
       <c r="F77" s="10" t="inlineStr">
         <is>
-          <t>ボランティア登録・活動見学のご案内</t>
+          <t>添えるカードをつくる</t>
         </is>
       </c>
       <c r="G77" s="26" t="inlineStr">
         <is>
-          <t>用紙を横に置いておく。その場で書いて帰れるように</t>
+          <t>「次回は◯月◯日です」「お問い合わせはボランティアセンターへ」。次につながる一言を入れる</t>
         </is>
       </c>
       <c r="H77" s="27" t="n"/>
@@ -5285,17 +5313,17 @@
       </c>
       <c r="E78" s="26" t="inlineStr">
         <is>
-          <t>F 会場に貼る表示物</t>
+          <t>D 参加記念品</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>町でいま動いている活動の紹介パネル</t>
+          <t>袋詰めをする</t>
         </is>
       </c>
       <c r="G78" s="26" t="inlineStr">
         <is>
-          <t>配食・見守り・サロン・除雪。写真を貼るだけでよい</t>
+          <t>記念品＋カード＋次回チラシをセットに。当日あわてないよう、前もって</t>
         </is>
       </c>
       <c r="H78" s="27" t="n"/>
@@ -5326,19 +5354,15 @@
       </c>
       <c r="E79" s="26" t="inlineStr">
         <is>
-          <t>G 盆栽ボランティアの準備</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>「育て方」の1枚をつくって印刷する</t>
-        </is>
-      </c>
-      <c r="G79" s="26" t="inlineStr">
-        <is>
-          <t>水やり／置き場所／冬の越し方／困ったときの連絡先。持ち帰ったあとも社協とつながる紙になります</t>
-        </is>
-      </c>
+          <t>参加者カード、筆記用具、クリップボード、受付名簿</t>
+        </is>
+      </c>
+      <c r="G79" s="26" t="n"/>
       <c r="H79" s="27" t="n"/>
       <c r="I79" s="27" t="inlineStr">
         <is>
@@ -5367,17 +5391,17 @@
       </c>
       <c r="E80" s="26" t="inlineStr">
         <is>
-          <t>G 盆栽ボランティアの準備</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>けがへの備えを確認する</t>
+          <t>テーブルクロス、花か観葉植物（1テーブルに1つ）</t>
         </is>
       </c>
       <c r="G80" s="26" t="inlineStr">
         <is>
-          <t>はさみを使います。保険の対象になるか、応急手当の担当は誰か</t>
+          <t>「会議」ではなく「カフェ」に見せるための、いちばん安い方法です</t>
         </is>
       </c>
       <c r="H80" s="27" t="n"/>
@@ -5408,17 +5432,17 @@
       </c>
       <c r="E81" s="26" t="inlineStr">
         <is>
-          <t>H 災ボラ体験の資料</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>進行台本をつくる</t>
+          <t>小さなスピーカー（BGM用・小音量）</t>
         </is>
       </c>
       <c r="G81" s="26" t="inlineStr">
         <is>
-          <t>誰がどの役をやり、何を言うか。参加者が少なかった場合の縮め方も書いておく</t>
+          <t>沈黙が気にならなくなり、はじめての方が入りやすくなります</t>
         </is>
       </c>
       <c r="H81" s="27" t="n"/>
@@ -5449,17 +5473,17 @@
       </c>
       <c r="E82" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>役割分担表をつくる</t>
+          <t>救急箱、消毒、絆創膏、体温計、ティッシュ</t>
         </is>
       </c>
       <c r="G82" s="26" t="inlineStr">
         <is>
-          <t>受付／お茶／進行／盆栽の補助／災ボラ／記録・写真／片付け。ひとり2役までにする</t>
+          <t>盆栽ではさみを使うため、絆創膏は多めに</t>
         </is>
       </c>
       <c r="H82" s="27" t="n"/>
@@ -5490,19 +5514,15 @@
       </c>
       <c r="E83" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>進行台本と、分単位のタイムテーブルをつくる</t>
-        </is>
-      </c>
-      <c r="G83" s="26" t="inlineStr">
-        <is>
-          <t>盆栽と災ボラを入れると90分は窮屈です。どちらかを次回に回す判断も、ここで決めておく</t>
-        </is>
-      </c>
+          <t>カメラ（記録用）、予備の電池</t>
+        </is>
+      </c>
+      <c r="G83" s="26" t="n"/>
       <c r="H83" s="27" t="n"/>
       <c r="I83" s="27" t="inlineStr">
         <is>
@@ -5531,19 +5551,15 @@
       </c>
       <c r="E84" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>台本とレイアウト図を、関わる全員に配る</t>
-        </is>
-      </c>
-      <c r="G84" s="26" t="inlineStr">
-        <is>
-          <t>講師・世話人候補・協力者にも。当日はじめて渡さない</t>
-        </is>
-      </c>
+          <t>マスキングテープ、養生テープ、模造紙、はさみ、油性ペン</t>
+        </is>
+      </c>
+      <c r="G84" s="26" t="n"/>
       <c r="H84" s="27" t="n"/>
       <c r="I84" s="27" t="inlineStr">
         <is>
@@ -5572,17 +5588,17 @@
       </c>
       <c r="E85" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>前日準備（12/14 15:00〜）の段取りと担当を決める</t>
+          <t>盆栽コーナーの表示と、手順の掲示</t>
         </is>
       </c>
       <c r="G85" s="26" t="inlineStr">
         <is>
-          <t>会場設営、机いすの配置、掲示、資機材の搬入、盆栽コーナーの下ごしらえ、給湯の確認</t>
+          <t>「土を入れる → 苗を置く → 水をやる」を、写真かイラストで3ステップに</t>
         </is>
       </c>
       <c r="H85" s="27" t="n"/>
@@ -5613,17 +5629,17 @@
       </c>
       <c r="E86" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>9:30〜10:00の進め方を決める</t>
+          <t>災ボラ体験コーナーの表示（受付／ニーズ受付／マッチング／送り出しの4か所）</t>
         </is>
       </c>
       <c r="G86" s="26" t="inlineStr">
         <is>
-          <t>受付・お茶・あいさつ・本日の流れ・ひとこと自己紹介。ここで場があたたまるかが、その後を左右します</t>
+          <t>本物の災害ボランティアセンターと同じ順に並べる。これ自体が説明になります</t>
         </is>
       </c>
       <c r="H86" s="27" t="n"/>
@@ -5640,7 +5656,7 @@
         <v>83</v>
       </c>
       <c r="B87" s="33">
-        <f>使い方!$B$5-7</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C87" s="34">
@@ -5649,22 +5665,22 @@
       </c>
       <c r="D87" s="35" t="inlineStr">
         <is>
-          <t>1週前</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E87" s="26" t="inlineStr">
         <is>
-          <t>C チラシと広報</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>参加の見込み数をまとめる</t>
+          <t>次回のご案内（日付を大きく1枚）</t>
         </is>
       </c>
       <c r="G87" s="26" t="inlineStr">
         <is>
-          <t>茶菓・記念品・盆栽材料の数を決めるため。予備を3〜5人分みておく</t>
+          <t>帰りぎわに必ず目に入る位置へ</t>
         </is>
       </c>
       <c r="H87" s="27" t="n"/>
@@ -5681,7 +5697,7 @@
         <v>84</v>
       </c>
       <c r="B88" s="33">
-        <f>使い方!$B$5-7</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C88" s="34">
@@ -5690,22 +5706,22 @@
       </c>
       <c r="D88" s="35" t="inlineStr">
         <is>
-          <t>1週前</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E88" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>お菓子</t>
+          <t>ボランティア登録・活動見学のご案内</t>
         </is>
       </c>
       <c r="G88" s="26" t="inlineStr">
         <is>
-          <t>個包装で、原材料表示のあるもの。やわらかいものも用意する（入れ歯の方のため）</t>
+          <t>用紙を横に置いておく。その場で書いて帰れるように</t>
         </is>
       </c>
       <c r="H88" s="27" t="n"/>
@@ -5722,7 +5738,7 @@
         <v>85</v>
       </c>
       <c r="B89" s="33">
-        <f>使い方!$B$5-7</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C89" s="34">
@@ -5731,22 +5747,22 @@
       </c>
       <c r="D89" s="35" t="inlineStr">
         <is>
-          <t>1週前</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E89" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>F 会場に貼る表示物</t>
         </is>
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>動線のリハーサルをする（30分でよい）</t>
+          <t>町でいま動いている活動の紹介パネル</t>
         </is>
       </c>
       <c r="G89" s="26" t="inlineStr">
         <is>
-          <t>入口から受付、席、盆栽コーナー、手洗い、災ボラコーナーまで、実際に歩いてみる</t>
+          <t>配食・見守り・サロン・除雪。写真を貼るだけでよい</t>
         </is>
       </c>
       <c r="H89" s="27" t="n"/>
@@ -5763,7 +5779,7 @@
         <v>86</v>
       </c>
       <c r="B90" s="33">
-        <f>使い方!$B$5-1</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C90" s="34">
@@ -5772,22 +5788,22 @@
       </c>
       <c r="D90" s="35" t="inlineStr">
         <is>
-          <t>前日</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E90" s="26" t="inlineStr">
         <is>
-          <t>B 事務の手続き</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>会場使用料の支払い</t>
+          <t>「育て方」の1枚をつくって印刷する</t>
         </is>
       </c>
       <c r="G90" s="26" t="inlineStr">
         <is>
-          <t>参加費を取らないことになったため、釣り銭の準備は不要</t>
+          <t>水やり／置き場所／冬の越し方／困ったときの連絡先。持ち帰ったあとも社協とつながる紙になります</t>
         </is>
       </c>
       <c r="H90" s="27" t="n"/>
@@ -5804,7 +5820,7 @@
         <v>87</v>
       </c>
       <c r="B91" s="33">
-        <f>使い方!$B$5-1</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C91" s="34">
@@ -5813,22 +5829,22 @@
       </c>
       <c r="D91" s="35" t="inlineStr">
         <is>
-          <t>前日</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E91" s="26" t="inlineStr">
         <is>
-          <t>C チラシと広報</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>声をかけた方へリマインドの電話</t>
+          <t>けがへの備えを確認する</t>
         </is>
       </c>
       <c r="G91" s="26" t="inlineStr">
         <is>
-          <t>「明日お待ちしています」の一本で、来場がはっきり変わります</t>
+          <t>はさみを使います。保険の対象になるか、応急手当の担当は誰か</t>
         </is>
       </c>
       <c r="H91" s="27" t="n"/>
@@ -5845,7 +5861,7 @@
         <v>88</v>
       </c>
       <c r="B92" s="33">
-        <f>使い方!$B$5-1</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C92" s="34">
@@ -5854,22 +5870,22 @@
       </c>
       <c r="D92" s="35" t="inlineStr">
         <is>
-          <t>前日</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E92" s="26" t="inlineStr">
         <is>
-          <t>E カフェで使う備品</t>
+          <t>H 災ボラ体験の資料</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>積み込みリストで最終確認をする</t>
+          <t>進行台本をつくる</t>
         </is>
       </c>
       <c r="G92" s="26" t="inlineStr">
         <is>
-          <t>この欄をそのまま印刷して、チェックしながら積む</t>
+          <t>誰がどの役をやり、何を言うか。参加者が少なかった場合の縮め方も書いておく</t>
         </is>
       </c>
       <c r="H92" s="27" t="n"/>
@@ -5886,7 +5902,7 @@
         <v>89</v>
       </c>
       <c r="B93" s="33">
-        <f>使い方!$B$5-1</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C93" s="34">
@@ -5895,7 +5911,7 @@
       </c>
       <c r="D93" s="35" t="inlineStr">
         <is>
-          <t>前日</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E93" s="26" t="inlineStr">
@@ -5905,12 +5921,12 @@
       </c>
       <c r="F93" s="10" t="inlineStr">
         <is>
-          <t>積み込み</t>
+          <t>役割分担表をつくる</t>
         </is>
       </c>
       <c r="G93" s="26" t="inlineStr">
         <is>
-          <t>Eの備品リストと、盆栽の材料、災ボラの資料一式、表示物、記念品</t>
+          <t>受付／お茶／進行／盆栽の補助／災ボラ／記録・写真／片付け。ひとり2役までにする</t>
         </is>
       </c>
       <c r="H93" s="27" t="n"/>
@@ -5927,7 +5943,7 @@
         <v>90</v>
       </c>
       <c r="B94" s="33">
-        <f>使い方!$B$5+0</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C94" s="34">
@@ -5936,22 +5952,22 @@
       </c>
       <c r="D94" s="35" t="inlineStr">
         <is>
-          <t>当日</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E94" s="26" t="inlineStr">
         <is>
-          <t>G 盆栽ボランティアの準備</t>
+          <t>I 当日の運営</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>「この続きをやりたい人」の名簿をその場でつくる</t>
+          <t>進行台本と、分単位のタイムテーブルをつくる</t>
         </is>
       </c>
       <c r="G94" s="26" t="inlineStr">
         <is>
-          <t>庭木・鉢の手入れを手伝う活動へ。教えてくれた方にも、世話人として関わってもらえるか声をかける</t>
+          <t>盆栽と災ボラを入れると90分は窮屈です。どちらかを次回に回す判断も、ここで決めておく</t>
         </is>
       </c>
       <c r="H94" s="27" t="n"/>
@@ -5968,7 +5984,7 @@
         <v>91</v>
       </c>
       <c r="B95" s="33">
-        <f>使い方!$B$5+0</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C95" s="34">
@@ -5977,7 +5993,7 @@
       </c>
       <c r="D95" s="35" t="inlineStr">
         <is>
-          <t>当日</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E95" s="26" t="inlineStr">
@@ -5987,12 +6003,12 @@
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>開場90分前に集合。設営・掲示・給湯・受付準備</t>
+          <t>台本とレイアウト図を、関わる全員に配る</t>
         </is>
       </c>
       <c r="G95" s="26" t="inlineStr">
         <is>
-          <t>机といすの数を実際に数える。90分前でも足りないことがあります</t>
+          <t>講師・世話人候補・協力者にも。当日はじめて渡さない</t>
         </is>
       </c>
       <c r="H95" s="27" t="n"/>
@@ -6009,7 +6025,7 @@
         <v>92</v>
       </c>
       <c r="B96" s="33">
-        <f>使い方!$B$5+0</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C96" s="34">
@@ -6018,7 +6034,7 @@
       </c>
       <c r="D96" s="35" t="inlineStr">
         <is>
-          <t>当日</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E96" s="26" t="inlineStr">
@@ -6028,12 +6044,12 @@
       </c>
       <c r="F96" s="10" t="inlineStr">
         <is>
-          <t>はじめての方に、世話人か職員がひとりつく</t>
+          <t>前日準備（12/14 15:00〜）の段取りと担当を決める</t>
         </is>
       </c>
       <c r="G96" s="26" t="inlineStr">
         <is>
-          <t>いちばん大事な役です。担当を先に決めておく</t>
+          <t>会場設営、机いすの配置、掲示、資機材の搬入、盆栽コーナーの下ごしらえ、給湯の確認</t>
         </is>
       </c>
       <c r="H96" s="27" t="n"/>
@@ -6050,7 +6066,7 @@
         <v>93</v>
       </c>
       <c r="B97" s="33">
-        <f>使い方!$B$5+0</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C97" s="34">
@@ -6059,7 +6075,7 @@
       </c>
       <c r="D97" s="35" t="inlineStr">
         <is>
-          <t>当日</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E97" s="26" t="inlineStr">
@@ -6069,12 +6085,12 @@
       </c>
       <c r="F97" s="10" t="inlineStr">
         <is>
-          <t>記録をとる</t>
+          <t>9:30〜10:00の進め方を決める</t>
         </is>
       </c>
       <c r="G97" s="26" t="inlineStr">
         <is>
-          <t>参加者数／はじめて来た人／出た話題／気になった方／つないだ先／写真</t>
+          <t>受付・お茶・あいさつ・本日の流れ・ひとこと自己紹介。ここで場があたたまるかが、その後を左右します</t>
         </is>
       </c>
       <c r="H97" s="27" t="n"/>
@@ -6091,7 +6107,7 @@
         <v>94</v>
       </c>
       <c r="B98" s="33">
-        <f>使い方!$B$5+0</f>
+        <f>使い方!$B$5-14</f>
         <v/>
       </c>
       <c r="C98" s="34">
@@ -6100,20 +6116,24 @@
       </c>
       <c r="D98" s="35" t="inlineStr">
         <is>
-          <t>当日</t>
+          <t>2週前</t>
         </is>
       </c>
       <c r="E98" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>K 体験・展示コーナーの準備</t>
         </is>
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>「やってみたいこと」「出られる曜日」を書いて帰ってもらう</t>
-        </is>
-      </c>
-      <c r="G98" s="26" t="n"/>
+          <t>段ボールベッドの組み立てと解体を、職員で一度やってみる</t>
+        </is>
+      </c>
+      <c r="G98" s="26" t="inlineStr">
+        <is>
+          <t>当日説明できるようになるため。何分かかるかを測っておくと、体験の時間配分が決められます</t>
+        </is>
+      </c>
       <c r="H98" s="27" t="n"/>
       <c r="I98" s="27" t="inlineStr">
         <is>
@@ -6128,7 +6148,7 @@
         <v>95</v>
       </c>
       <c r="B99" s="33">
-        <f>使い方!$B$5+0</f>
+        <f>使い方!$B$5-7</f>
         <v/>
       </c>
       <c r="C99" s="34">
@@ -6137,22 +6157,22 @@
       </c>
       <c r="D99" s="35" t="inlineStr">
         <is>
-          <t>当日</t>
+          <t>1週前</t>
         </is>
       </c>
       <c r="E99" s="26" t="inlineStr">
         <is>
-          <t>I 当日の運営</t>
+          <t>C チラシと広報</t>
         </is>
       </c>
       <c r="F99" s="10" t="inlineStr">
         <is>
-          <t>終了後15分でふりかえり。次回に変えることを1つだけ決める</t>
+          <t>参加の見込み数をまとめる</t>
         </is>
       </c>
       <c r="G99" s="26" t="inlineStr">
         <is>
-          <t>その場で決めないと、次回まで持ち越されて忘れます</t>
+          <t>茶菓・記念品・盆栽材料の数を決めるため。予備を3〜5人分みておく</t>
         </is>
       </c>
       <c r="H99" s="27" t="n"/>
@@ -6169,7 +6189,7 @@
         <v>96</v>
       </c>
       <c r="B100" s="33">
-        <f>使い方!$B$5+0</f>
+        <f>使い方!$B$5-7</f>
         <v/>
       </c>
       <c r="C100" s="34">
@@ -6178,22 +6198,22 @@
       </c>
       <c r="D100" s="35" t="inlineStr">
         <is>
-          <t>当日中</t>
+          <t>1週前</t>
         </is>
       </c>
       <c r="E100" s="26" t="inlineStr">
         <is>
-          <t>J 終わったあと</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>開催記録を書く</t>
+          <t>お菓子</t>
         </is>
       </c>
       <c r="G100" s="26" t="inlineStr">
         <is>
-          <t>記憶が新しいうちに。第1期以降の評価は、この記録の積み重ねでしか出せません</t>
+          <t>個包装で、原材料表示のあるもの。やわらかいものも用意する（入れ歯の方のため）</t>
         </is>
       </c>
       <c r="H100" s="27" t="n"/>
@@ -6210,7 +6230,7 @@
         <v>97</v>
       </c>
       <c r="B101" s="33">
-        <f>使い方!$B$5+3</f>
+        <f>使い方!$B$5-7</f>
         <v/>
       </c>
       <c r="C101" s="34">
@@ -6219,22 +6239,22 @@
       </c>
       <c r="D101" s="35" t="inlineStr">
         <is>
-          <t>3日以内</t>
+          <t>1週前</t>
         </is>
       </c>
       <c r="E101" s="26" t="inlineStr">
         <is>
-          <t>J 終わったあと</t>
+          <t>I 当日の運営</t>
         </is>
       </c>
       <c r="F101" s="10" t="inlineStr">
         <is>
-          <t>講師・協力者・会場へお礼</t>
+          <t>動線のリハーサルをする（30分でよい）</t>
         </is>
       </c>
       <c r="G101" s="26" t="inlineStr">
         <is>
-          <t>盆栽を教えてくれた方には、当日の写真を添えて</t>
+          <t>入口から受付、席、盆栽コーナー、手洗い、災ボラコーナーまで、実際に歩いてみる</t>
         </is>
       </c>
       <c r="H101" s="27" t="n"/>
@@ -6251,7 +6271,7 @@
         <v>98</v>
       </c>
       <c r="B102" s="33">
-        <f>使い方!$B$5+7</f>
+        <f>使い方!$B$5-1</f>
         <v/>
       </c>
       <c r="C102" s="34">
@@ -6260,22 +6280,22 @@
       </c>
       <c r="D102" s="35" t="inlineStr">
         <is>
-          <t>1週以内</t>
+          <t>前日</t>
         </is>
       </c>
       <c r="E102" s="26" t="inlineStr">
         <is>
-          <t>J 終わったあと</t>
+          <t>B 事務の手続き</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>写真を整理し、使ってよいものを選ぶ</t>
+          <t>会場使用料の支払い</t>
         </is>
       </c>
       <c r="G102" s="26" t="inlineStr">
         <is>
-          <t>写りたくないと申し出た方が入っていないか、必ず確認する</t>
+          <t>参加費を取らないことになったため、釣り銭の準備は不要</t>
         </is>
       </c>
       <c r="H102" s="27" t="n"/>
@@ -6292,7 +6312,7 @@
         <v>99</v>
       </c>
       <c r="B103" s="33">
-        <f>使い方!$B$5+7</f>
+        <f>使い方!$B$5-1</f>
         <v/>
       </c>
       <c r="C103" s="34">
@@ -6301,20 +6321,24 @@
       </c>
       <c r="D103" s="35" t="inlineStr">
         <is>
-          <t>1週以内</t>
+          <t>前日</t>
         </is>
       </c>
       <c r="E103" s="26" t="inlineStr">
         <is>
-          <t>J 終わったあと</t>
+          <t>C チラシと広報</t>
         </is>
       </c>
       <c r="F103" s="10" t="inlineStr">
         <is>
-          <t>支出を精算する</t>
-        </is>
-      </c>
-      <c r="G103" s="26" t="n"/>
+          <t>声をかけた方へリマインドの電話</t>
+        </is>
+      </c>
+      <c r="G103" s="26" t="inlineStr">
+        <is>
+          <t>「明日お待ちしています」の一本で、来場がはっきり変わります</t>
+        </is>
+      </c>
       <c r="H103" s="27" t="n"/>
       <c r="I103" s="27" t="inlineStr">
         <is>
@@ -6329,7 +6353,7 @@
         <v>100</v>
       </c>
       <c r="B104" s="33">
-        <f>使い方!$B$5+7</f>
+        <f>使い方!$B$5-1</f>
         <v/>
       </c>
       <c r="C104" s="34">
@@ -6338,22 +6362,22 @@
       </c>
       <c r="D104" s="35" t="inlineStr">
         <is>
-          <t>1週以内</t>
+          <t>前日</t>
         </is>
       </c>
       <c r="E104" s="26" t="inlineStr">
         <is>
-          <t>J 終わったあと</t>
+          <t>E カフェで使う備品</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>参加者へ次回のお知らせ</t>
+          <t>積み込みリストで最終確認をする</t>
         </is>
       </c>
       <c r="G104" s="26" t="inlineStr">
         <is>
-          <t>希望された方へ。第2回の日付だけでも早く伝える</t>
+          <t>この欄をそのまま印刷して、チェックしながら積む</t>
         </is>
       </c>
       <c r="H104" s="27" t="n"/>
@@ -6370,7 +6394,7 @@
         <v>101</v>
       </c>
       <c r="B105" s="33">
-        <f>使い方!$B$5+14</f>
+        <f>使い方!$B$5-1</f>
         <v/>
       </c>
       <c r="C105" s="34">
@@ -6379,22 +6403,22 @@
       </c>
       <c r="D105" s="35" t="inlineStr">
         <is>
-          <t>2週以内</t>
+          <t>前日</t>
         </is>
       </c>
       <c r="E105" s="26" t="inlineStr">
         <is>
-          <t>J 終わったあと</t>
+          <t>I 当日の運営</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>運営委員会・事務局へ報告する</t>
+          <t>積み込み</t>
         </is>
       </c>
       <c r="G105" s="26" t="inlineStr">
         <is>
-          <t>人数だけでなく、その日に生まれた会話や関係も書く</t>
+          <t>Eの備品リストと、盆栽の材料、災ボラの資料一式、表示物、記念品</t>
         </is>
       </c>
       <c r="H105" s="27" t="n"/>
@@ -6404,18 +6428,14 @@
         </is>
       </c>
       <c r="J105" s="36" t="n"/>
-      <c r="K105" s="37" t="inlineStr">
-        <is>
-          <t>12月29日は年末休みの可能性。12月28日までに</t>
-        </is>
-      </c>
+      <c r="K105" s="37" t="n"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="32" t="n">
         <v>102</v>
       </c>
       <c r="B106" s="33">
-        <f>使い方!$B$5+14</f>
+        <f>使い方!$B$5+0</f>
         <v/>
       </c>
       <c r="C106" s="34">
@@ -6424,22 +6444,22 @@
       </c>
       <c r="D106" s="35" t="inlineStr">
         <is>
-          <t>2週以内</t>
+          <t>当日</t>
         </is>
       </c>
       <c r="E106" s="26" t="inlineStr">
         <is>
-          <t>J 終わったあと</t>
+          <t>G 盆栽ボランティアの準備</t>
         </is>
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>参加者カードを整理し、保管する</t>
+          <t>「この続きをやりたい人」の名簿をその場でつくる</t>
         </is>
       </c>
       <c r="G106" s="26" t="inlineStr">
         <is>
-          <t>次回「カフェ以外で会いましたか」を聞くための土台になります</t>
+          <t>庭木・鉢の手入れを手伝う活動へ。教えてくれた方にも、世話人として関わってもらえるか声をかける</t>
         </is>
       </c>
       <c r="H106" s="27" t="n"/>
@@ -6449,18 +6469,14 @@
         </is>
       </c>
       <c r="J106" s="36" t="n"/>
-      <c r="K106" s="37" t="inlineStr">
-        <is>
-          <t>12月29日は年末休みの可能性。12月28日までに</t>
-        </is>
-      </c>
+      <c r="K106" s="37" t="n"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="32" t="n">
         <v>103</v>
       </c>
       <c r="B107" s="33">
-        <f>使い方!$B$5+14</f>
+        <f>使い方!$B$5+0</f>
         <v/>
       </c>
       <c r="C107" s="34">
@@ -6469,22 +6485,22 @@
       </c>
       <c r="D107" s="35" t="inlineStr">
         <is>
-          <t>2週以内</t>
+          <t>当日</t>
         </is>
       </c>
       <c r="E107" s="26" t="inlineStr">
         <is>
-          <t>J 終わったあと</t>
+          <t>I 当日の運営</t>
         </is>
       </c>
       <c r="F107" s="10" t="inlineStr">
         <is>
-          <t>盆栽の続きを希望した方へ連絡する</t>
+          <t>開場90分前に集合。設営・掲示・給湯・受付準備</t>
         </is>
       </c>
       <c r="G107" s="26" t="inlineStr">
         <is>
-          <t>熱があるうちに。2週間空くと、気持ちは戻ってしまいます</t>
+          <t>机といすの数を実際に数える。90分前でも足りないことがあります</t>
         </is>
       </c>
       <c r="H107" s="27" t="n"/>
@@ -6494,15 +6510,507 @@
         </is>
       </c>
       <c r="J107" s="36" t="n"/>
-      <c r="K107" s="37" t="inlineStr">
+      <c r="K107" s="37" t="n"/>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="32" t="n">
+        <v>104</v>
+      </c>
+      <c r="B108" s="33">
+        <f>使い方!$B$5+0</f>
+        <v/>
+      </c>
+      <c r="C108" s="34">
+        <f>CHOOSE(WEEKDAY(B108),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D108" s="35" t="inlineStr">
+        <is>
+          <t>当日</t>
+        </is>
+      </c>
+      <c r="E108" s="26" t="inlineStr">
+        <is>
+          <t>I 当日の運営</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>はじめての方に、世話人か職員がひとりつく</t>
+        </is>
+      </c>
+      <c r="G108" s="26" t="inlineStr">
+        <is>
+          <t>いちばん大事な役です。担当を先に決めておく</t>
+        </is>
+      </c>
+      <c r="H108" s="27" t="n"/>
+      <c r="I108" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J108" s="36" t="n"/>
+      <c r="K108" s="37" t="n"/>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="32" t="n">
+        <v>105</v>
+      </c>
+      <c r="B109" s="33">
+        <f>使い方!$B$5+0</f>
+        <v/>
+      </c>
+      <c r="C109" s="34">
+        <f>CHOOSE(WEEKDAY(B109),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D109" s="35" t="inlineStr">
+        <is>
+          <t>当日</t>
+        </is>
+      </c>
+      <c r="E109" s="26" t="inlineStr">
+        <is>
+          <t>I 当日の運営</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>記録をとる</t>
+        </is>
+      </c>
+      <c r="G109" s="26" t="inlineStr">
+        <is>
+          <t>参加者数／はじめて来た人／出た話題／気になった方／つないだ先／写真</t>
+        </is>
+      </c>
+      <c r="H109" s="27" t="n"/>
+      <c r="I109" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J109" s="36" t="n"/>
+      <c r="K109" s="37" t="n"/>
+    </row>
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="32" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="33">
+        <f>使い方!$B$5+0</f>
+        <v/>
+      </c>
+      <c r="C110" s="34">
+        <f>CHOOSE(WEEKDAY(B110),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D110" s="35" t="inlineStr">
+        <is>
+          <t>当日</t>
+        </is>
+      </c>
+      <c r="E110" s="26" t="inlineStr">
+        <is>
+          <t>I 当日の運営</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>「やってみたいこと」「出られる曜日」を書いて帰ってもらう</t>
+        </is>
+      </c>
+      <c r="G110" s="26" t="n"/>
+      <c r="H110" s="27" t="n"/>
+      <c r="I110" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J110" s="36" t="n"/>
+      <c r="K110" s="37" t="n"/>
+    </row>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="32" t="n">
+        <v>107</v>
+      </c>
+      <c r="B111" s="33">
+        <f>使い方!$B$5+0</f>
+        <v/>
+      </c>
+      <c r="C111" s="34">
+        <f>CHOOSE(WEEKDAY(B111),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D111" s="35" t="inlineStr">
+        <is>
+          <t>当日</t>
+        </is>
+      </c>
+      <c r="E111" s="26" t="inlineStr">
+        <is>
+          <t>I 当日の運営</t>
+        </is>
+      </c>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>終了後15分でふりかえり。次回に変えることを1つだけ決める</t>
+        </is>
+      </c>
+      <c r="G111" s="26" t="inlineStr">
+        <is>
+          <t>その場で決めないと、次回まで持ち越されて忘れます</t>
+        </is>
+      </c>
+      <c r="H111" s="27" t="n"/>
+      <c r="I111" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J111" s="36" t="n"/>
+      <c r="K111" s="37" t="n"/>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="32" t="n">
+        <v>108</v>
+      </c>
+      <c r="B112" s="33">
+        <f>使い方!$B$5+0</f>
+        <v/>
+      </c>
+      <c r="C112" s="34">
+        <f>CHOOSE(WEEKDAY(B112),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D112" s="35" t="inlineStr">
+        <is>
+          <t>当日中</t>
+        </is>
+      </c>
+      <c r="E112" s="26" t="inlineStr">
+        <is>
+          <t>J 終わったあと</t>
+        </is>
+      </c>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>開催記録を書く</t>
+        </is>
+      </c>
+      <c r="G112" s="26" t="inlineStr">
+        <is>
+          <t>記憶が新しいうちに。第1期以降の評価は、この記録の積み重ねでしか出せません</t>
+        </is>
+      </c>
+      <c r="H112" s="27" t="n"/>
+      <c r="I112" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J112" s="36" t="n"/>
+      <c r="K112" s="37" t="n"/>
+    </row>
+    <row r="113" ht="30" customHeight="1">
+      <c r="A113" s="32" t="n">
+        <v>109</v>
+      </c>
+      <c r="B113" s="33">
+        <f>使い方!$B$5+3</f>
+        <v/>
+      </c>
+      <c r="C113" s="34">
+        <f>CHOOSE(WEEKDAY(B113),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D113" s="35" t="inlineStr">
+        <is>
+          <t>3日以内</t>
+        </is>
+      </c>
+      <c r="E113" s="26" t="inlineStr">
+        <is>
+          <t>J 終わったあと</t>
+        </is>
+      </c>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>講師・協力者・会場へお礼</t>
+        </is>
+      </c>
+      <c r="G113" s="26" t="inlineStr">
+        <is>
+          <t>盆栽を教えてくれた方には、当日の写真を添えて</t>
+        </is>
+      </c>
+      <c r="H113" s="27" t="n"/>
+      <c r="I113" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J113" s="36" t="n"/>
+      <c r="K113" s="37" t="n"/>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="32" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="33">
+        <f>使い方!$B$5+7</f>
+        <v/>
+      </c>
+      <c r="C114" s="34">
+        <f>CHOOSE(WEEKDAY(B114),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D114" s="35" t="inlineStr">
+        <is>
+          <t>1週以内</t>
+        </is>
+      </c>
+      <c r="E114" s="26" t="inlineStr">
+        <is>
+          <t>J 終わったあと</t>
+        </is>
+      </c>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>写真を整理し、使ってよいものを選ぶ</t>
+        </is>
+      </c>
+      <c r="G114" s="26" t="inlineStr">
+        <is>
+          <t>写りたくないと申し出た方が入っていないか、必ず確認する</t>
+        </is>
+      </c>
+      <c r="H114" s="27" t="n"/>
+      <c r="I114" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J114" s="36" t="n"/>
+      <c r="K114" s="37" t="n"/>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="A115" s="32" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="33">
+        <f>使い方!$B$5+7</f>
+        <v/>
+      </c>
+      <c r="C115" s="34">
+        <f>CHOOSE(WEEKDAY(B115),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D115" s="35" t="inlineStr">
+        <is>
+          <t>1週以内</t>
+        </is>
+      </c>
+      <c r="E115" s="26" t="inlineStr">
+        <is>
+          <t>J 終わったあと</t>
+        </is>
+      </c>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>支出を精算する</t>
+        </is>
+      </c>
+      <c r="G115" s="26" t="n"/>
+      <c r="H115" s="27" t="n"/>
+      <c r="I115" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J115" s="36" t="n"/>
+      <c r="K115" s="37" t="n"/>
+    </row>
+    <row r="116" ht="30" customHeight="1">
+      <c r="A116" s="32" t="n">
+        <v>112</v>
+      </c>
+      <c r="B116" s="33">
+        <f>使い方!$B$5+7</f>
+        <v/>
+      </c>
+      <c r="C116" s="34">
+        <f>CHOOSE(WEEKDAY(B116),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D116" s="35" t="inlineStr">
+        <is>
+          <t>1週以内</t>
+        </is>
+      </c>
+      <c r="E116" s="26" t="inlineStr">
+        <is>
+          <t>J 終わったあと</t>
+        </is>
+      </c>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>参加者へ次回のお知らせ</t>
+        </is>
+      </c>
+      <c r="G116" s="26" t="inlineStr">
+        <is>
+          <t>希望された方へ。第2回の日付だけでも早く伝える</t>
+        </is>
+      </c>
+      <c r="H116" s="27" t="n"/>
+      <c r="I116" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J116" s="36" t="n"/>
+      <c r="K116" s="37" t="n"/>
+    </row>
+    <row r="117" ht="30" customHeight="1">
+      <c r="A117" s="32" t="n">
+        <v>113</v>
+      </c>
+      <c r="B117" s="33">
+        <f>使い方!$B$5+14</f>
+        <v/>
+      </c>
+      <c r="C117" s="34">
+        <f>CHOOSE(WEEKDAY(B117),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D117" s="35" t="inlineStr">
+        <is>
+          <t>2週以内</t>
+        </is>
+      </c>
+      <c r="E117" s="26" t="inlineStr">
+        <is>
+          <t>J 終わったあと</t>
+        </is>
+      </c>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>運営委員会・事務局へ報告する</t>
+        </is>
+      </c>
+      <c r="G117" s="26" t="inlineStr">
+        <is>
+          <t>人数だけでなく、その日に生まれた会話や関係も書く</t>
+        </is>
+      </c>
+      <c r="H117" s="27" t="n"/>
+      <c r="I117" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J117" s="36" t="n"/>
+      <c r="K117" s="37" t="inlineStr">
         <is>
           <t>12月29日は年末休みの可能性。12月28日までに</t>
         </is>
       </c>
     </row>
+    <row r="118" ht="30" customHeight="1">
+      <c r="A118" s="32" t="n">
+        <v>114</v>
+      </c>
+      <c r="B118" s="33">
+        <f>使い方!$B$5+14</f>
+        <v/>
+      </c>
+      <c r="C118" s="34">
+        <f>CHOOSE(WEEKDAY(B118),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D118" s="35" t="inlineStr">
+        <is>
+          <t>2週以内</t>
+        </is>
+      </c>
+      <c r="E118" s="26" t="inlineStr">
+        <is>
+          <t>J 終わったあと</t>
+        </is>
+      </c>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>参加者カードを整理し、保管する</t>
+        </is>
+      </c>
+      <c r="G118" s="26" t="inlineStr">
+        <is>
+          <t>次回「カフェ以外で会いましたか」を聞くための土台になります</t>
+        </is>
+      </c>
+      <c r="H118" s="27" t="n"/>
+      <c r="I118" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J118" s="36" t="n"/>
+      <c r="K118" s="37" t="inlineStr">
+        <is>
+          <t>12月29日は年末休みの可能性。12月28日までに</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="32" t="n">
+        <v>115</v>
+      </c>
+      <c r="B119" s="33">
+        <f>使い方!$B$5+14</f>
+        <v/>
+      </c>
+      <c r="C119" s="34">
+        <f>CHOOSE(WEEKDAY(B119),"日","月","火","水","木","金","土")</f>
+        <v/>
+      </c>
+      <c r="D119" s="35" t="inlineStr">
+        <is>
+          <t>2週以内</t>
+        </is>
+      </c>
+      <c r="E119" s="26" t="inlineStr">
+        <is>
+          <t>J 終わったあと</t>
+        </is>
+      </c>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>盆栽の続きを希望した方へ連絡する</t>
+        </is>
+      </c>
+      <c r="G119" s="26" t="inlineStr">
+        <is>
+          <t>熱があるうちに。2週間空くと、気持ちは戻ってしまいます</t>
+        </is>
+      </c>
+      <c r="H119" s="27" t="n"/>
+      <c r="I119" s="27" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="J119" s="36" t="n"/>
+      <c r="K119" s="37" t="inlineStr">
+        <is>
+          <t>12月29日は年末休みの可能性。12月28日までに</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K107"/>
-  <conditionalFormatting sqref="A5:K107">
+  <autoFilter ref="A4:K119"/>
+  <conditionalFormatting sqref="A5:K119">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>AND($B5&lt;TODAY(),$I5&lt;&gt;"完了",$I5&lt;&gt;"対象外")</formula>
     </cfRule>
@@ -6511,7 +7019,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I107" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="状況" prompt="選んでください" type="list">
+    <dataValidation sqref="I5:I119" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="状況" prompt="選んでください" type="list">
       <formula1>"未着手,準備中,完了,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6615,11 +7123,11 @@
         </is>
       </c>
       <c r="E5" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C5)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C5)</f>
         <v/>
       </c>
       <c r="F5" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C5,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C5,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G5" s="41">
@@ -6652,11 +7160,11 @@
         </is>
       </c>
       <c r="E6" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C6)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C6)</f>
         <v/>
       </c>
       <c r="F6" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C6,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C6,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G6" s="41">
@@ -6689,11 +7197,11 @@
         </is>
       </c>
       <c r="E7" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C7)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C7)</f>
         <v/>
       </c>
       <c r="F7" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C7,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C7,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G7" s="41">
@@ -6726,11 +7234,11 @@
         </is>
       </c>
       <c r="E8" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C8)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C8)</f>
         <v/>
       </c>
       <c r="F8" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C8,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C8,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G8" s="41">
@@ -6755,15 +7263,15 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>予算50,000円の配分を決める。参加記念品を決める。盆栽の内容と材料の数量を決める</t>
+          <t>予算の配分を決める。段ボールベッドの借用・台数、防災グッズの購入リスト、防災バッグの借用を依頼する</t>
         </is>
       </c>
       <c r="E9" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C9)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C9)</f>
         <v/>
       </c>
       <c r="F9" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C9,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C9,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G9" s="41">
@@ -6792,22 +7300,26 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>講座の構成と話す人を決める。防災士への応援依頼文をつくって出す</t>
+          <t>講座の構成と話す人を決める。防災士へ依頼文を出す。防災グッズと段ボールベッド不足分を発注する</t>
         </is>
       </c>
       <c r="E10" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C10)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C10)</f>
         <v/>
       </c>
       <c r="F10" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C10,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C10,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G10" s="41">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="H10" s="43" t="n"/>
+      <c r="H10" s="42" t="inlineStr">
+        <is>
+          <t>発注の納期に注意</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="38">
@@ -6829,11 +7341,11 @@
         </is>
       </c>
       <c r="E11" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C11)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C11)</f>
         <v/>
       </c>
       <c r="F11" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C11,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C11,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G11" s="41">
@@ -6862,15 +7374,15 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>直接声かけを始める（まず20人）。掲示を各所へ。表示物と講座資料をつくる</t>
+          <t>直接声かけを始める。掲示を各所へ。表示物・講座資料・各コーナーの説明札をつくる</t>
         </is>
       </c>
       <c r="E12" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C12)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C12)</f>
         <v/>
       </c>
       <c r="F12" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C12,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C12,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G12" s="41">
@@ -6899,15 +7411,15 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>役割分担と進行台本。レイアウト図。前日準備の段取り。記念品の袋詰め</t>
+          <t>役割分担と進行台本。レイアウト図。段ボールベッドの組み立て練習。記念品の袋詰め</t>
         </is>
       </c>
       <c r="E13" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C13)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C13)</f>
         <v/>
       </c>
       <c r="F13" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C13,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C13,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G13" s="41">
@@ -6940,11 +7452,11 @@
         </is>
       </c>
       <c r="E14" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C14)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C14)</f>
         <v/>
       </c>
       <c r="F14" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C14,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C14,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G14" s="41">
@@ -6973,11 +7485,11 @@
         </is>
       </c>
       <c r="E15" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C15)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C15)</f>
         <v/>
       </c>
       <c r="F15" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C15,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C15,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G15" s="41">
@@ -7010,11 +7522,11 @@
         </is>
       </c>
       <c r="E16" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C16)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C16)</f>
         <v/>
       </c>
       <c r="F16" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C16,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C16,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G16" s="41">
@@ -7047,11 +7559,11 @@
         </is>
       </c>
       <c r="E17" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C17)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C17)</f>
         <v/>
       </c>
       <c r="F17" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C17,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C17,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G17" s="41">
@@ -7084,11 +7596,11 @@
         </is>
       </c>
       <c r="E18" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C18)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C18)</f>
         <v/>
       </c>
       <c r="F18" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C18,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C18,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G18" s="41">
@@ -7121,11 +7633,11 @@
         </is>
       </c>
       <c r="E19" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C19)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C19)</f>
         <v/>
       </c>
       <c r="F19" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C19,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C19,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G19" s="41">
@@ -7158,11 +7670,11 @@
         </is>
       </c>
       <c r="E20" s="24">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$C20)</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$C20)</f>
         <v/>
       </c>
       <c r="F20" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$C20,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$C20,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="G20" s="41">
@@ -7215,7 +7727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7262,7 +7774,7 @@
         </is>
       </c>
       <c r="B5" s="48" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
@@ -7310,11 +7822,11 @@
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>お茶・コーヒー・お菓子。見込み30人＋予備5人分</t>
+          <t>お茶・コーヒー・お菓子。定員50人＋予備5人分</t>
         </is>
       </c>
       <c r="C8" s="49" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D8" s="49">
         <f>$B$5+5</f>
@@ -7342,7 +7854,7 @@
         </is>
       </c>
       <c r="C9" s="49" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="D9" s="49">
         <f>$B$5+5</f>
@@ -7361,19 +7873,19 @@
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>盆栽の材料</t>
+          <t>最新の防災グッズ</t>
         </is>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>苗・鉢・用土・鉢底ネット・化粧砂。1人1セット</t>
+          <t>展示用に購入する。さわれるようにして並べる</t>
         </is>
       </c>
       <c r="C10" s="49" t="n">
-        <v>700</v>
+        <v>10000</v>
       </c>
       <c r="D10" s="49" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E10" s="50">
         <f>C10*D10</f>
@@ -7381,26 +7893,26 @@
       </c>
       <c r="F10" s="51" t="inlineStr">
         <is>
-          <t>20セット。参加者全員分でなく、希望者分で足ります</t>
+          <t>「見たことがない」「さわってみたい」と思えるものを優先する</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>盆栽の道具・汚れ対策</t>
+          <t>段ボールベッド</t>
         </is>
       </c>
       <c r="B11" s="26" t="inlineStr">
         <is>
-          <t>剪定ばさみ3〜4本、じょうろ、ブルーシート、軍手、雑巾</t>
+          <t>町の備蓄から借り、不足分だけ購入する</t>
         </is>
       </c>
       <c r="C11" s="49" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="D11" s="49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="50">
         <f>C11*D11</f>
@@ -7408,26 +7920,26 @@
       </c>
       <c r="F11" s="51" t="inlineStr">
         <is>
-          <t>はさみは人数分要りません。回して使います</t>
+          <t>借用でまかなう想定のため数量0。購入するなら台数を入れてください（1台あたり約3,000円）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>印刷</t>
+          <t>盆栽の材料</t>
         </is>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>チラシ、講座の配布資料、参加者カード、表示物</t>
+          <t>苗・鉢・用土・鉢底ネット・化粧砂。1人1セット</t>
         </is>
       </c>
       <c r="C12" s="49" t="n">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="D12" s="49" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E12" s="50">
         <f>C12*D12</f>
@@ -7435,23 +7947,23 @@
       </c>
       <c r="F12" s="51" t="inlineStr">
         <is>
-          <t>表示物は模造紙とペンで手書きでも十分です</t>
+          <t>希望者15人分。参加者全員分は予算に入りません</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>消耗品</t>
+          <t>盆栽の道具・汚れ対策</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>名札、紙コップ、紙皿、おしぼり、ゴミ袋、文具</t>
+          <t>剪定ばさみ3〜4本、じょうろ、ブルーシート、軍手、雑巾</t>
         </is>
       </c>
       <c r="C13" s="49" t="n">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="D13" s="49" t="n">
         <v>1</v>
@@ -7460,17 +7972,21 @@
         <f>C13*D13</f>
         <v/>
       </c>
-      <c r="F13" s="51" t="n"/>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>はさみは人数分要りません。回して使います</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>講師・協力者へのお礼</t>
+          <t>印刷</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>盆栽を教えてくれる方、講座を手伝ってくれる方へ</t>
+          <t>チラシ、講座の配布資料、参加者カード、表示物、各コーナーの説明札</t>
         </is>
       </c>
       <c r="C14" s="49" t="n">
@@ -7485,60 +8001,110 @@
       </c>
       <c r="F14" s="51" t="inlineStr">
         <is>
+          <t>説明札は模造紙とペンで手書きでも十分です</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>消耗品</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>名札、紙コップ、紙皿、おしぼり、ゴミ袋、文具</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="50">
+        <f>C15*D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="51" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>講師・協力者へのお礼</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>高橋文之さん、防災士、配食ボランティアのみなさんへ</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D16" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="50">
+        <f>C16*D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="51" t="inlineStr">
+        <is>
           <t>品物にするか謝金にするか、規程を確認してください</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="23" t="n"/>
-      <c r="B15" s="52" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="23" t="n"/>
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="53">
-        <f>SUM(E8:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="23" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n"/>
-      <c r="B16" s="52" t="inlineStr">
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="53">
+        <f>SUM(E8:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="23" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n"/>
+      <c r="B18" s="52" t="inlineStr">
         <is>
           <t>予算の残り</t>
         </is>
       </c>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="54">
-        <f>$B$4-E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="55" t="inlineStr">
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="54">
+        <f>$B$4-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="55" t="inlineStr">
         <is>
           <t>マイナスになったら、どこかを削ってください</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>※ 単価・数量はすべて、この表をつくった時点での仮置きです。実際の見積に置き換えてください。総額50,000円は9/2時点で示された額です。参加費は取らないことになったため（9/4）、収入はありません。盆栽の材料は希望者20人分で組んでいます。参加者35人分にすると10,500円増え、予算を超えます。この配分では合計48,000円、残り2,000円です。当日の買い足しに備えて、あえて残してあります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>※ 単価・数量はすべて、この表をつくった時点での仮置きです。実際の見積に置き換えてください。総額50,000円は9/2時点で示された額です。参加費は取らないことになったため（9/4）、収入はありません。チラシで定員が50人になったため、茶菓と記念品を55人分で組み直し、単価を下げました。段ボールベッドは町の備蓄から借りる想定で数量0にしています。不足分を買う場合は1台あたり約3,000円かかり、その分は記念品の単価か、盆栽の材料の数を減らして捻出することになります。防災バッグは役場総務課防災対策室からの借用のため、費用は見込んでいません。盆栽の材料は希望者15人分で組んでいます。合計と残りは下の行に自動で出ます。残りがマイナスになったら、どこかを削ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A18:F20"/>
+    <mergeCell ref="A20:F22"/>
   </mergeCells>
-  <conditionalFormatting sqref="E16">
+  <conditionalFormatting sqref="E18">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>$E$16&lt;0</formula>
+      <formula>$E$18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7629,11 +8195,11 @@
         </is>
       </c>
       <c r="B5" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A5,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A5,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C5" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A5)-B5</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A5)-B5</f>
         <v/>
       </c>
       <c r="D5" s="57">
@@ -7646,11 +8212,11 @@
         </is>
       </c>
       <c r="G5" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F5,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F5,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H5" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F5)-G5</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F5)-G5</f>
         <v/>
       </c>
       <c r="I5" s="57">
@@ -7665,11 +8231,11 @@
         </is>
       </c>
       <c r="B6" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A6,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A6,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C6" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A6)-B6</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A6)-B6</f>
         <v/>
       </c>
       <c r="D6" s="57">
@@ -7682,11 +8248,11 @@
         </is>
       </c>
       <c r="G6" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F6,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F6,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H6" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F6)-G6</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F6)-G6</f>
         <v/>
       </c>
       <c r="I6" s="57">
@@ -7701,11 +8267,11 @@
         </is>
       </c>
       <c r="B7" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A7,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A7,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C7" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A7)-B7</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A7)-B7</f>
         <v/>
       </c>
       <c r="D7" s="57">
@@ -7718,11 +8284,11 @@
         </is>
       </c>
       <c r="G7" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F7,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F7,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H7" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F7)-G7</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F7)-G7</f>
         <v/>
       </c>
       <c r="I7" s="57">
@@ -7737,11 +8303,11 @@
         </is>
       </c>
       <c r="B8" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A8,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A8,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C8" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A8)-B8</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A8)-B8</f>
         <v/>
       </c>
       <c r="D8" s="57">
@@ -7754,11 +8320,11 @@
         </is>
       </c>
       <c r="G8" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F8,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F8,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H8" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F8)-G8</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F8)-G8</f>
         <v/>
       </c>
       <c r="I8" s="57">
@@ -7773,11 +8339,11 @@
         </is>
       </c>
       <c r="B9" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A9,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A9,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C9" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A9)-B9</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A9)-B9</f>
         <v/>
       </c>
       <c r="D9" s="57">
@@ -7790,11 +8356,11 @@
         </is>
       </c>
       <c r="G9" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F9,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F9,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H9" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F9)-G9</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F9)-G9</f>
         <v/>
       </c>
       <c r="I9" s="57">
@@ -7809,11 +8375,11 @@
         </is>
       </c>
       <c r="B10" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A10,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A10,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C10" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A10)-B10</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A10)-B10</f>
         <v/>
       </c>
       <c r="D10" s="57">
@@ -7826,11 +8392,11 @@
         </is>
       </c>
       <c r="G10" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F10,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F10,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H10" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F10)-G10</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F10)-G10</f>
         <v/>
       </c>
       <c r="I10" s="57">
@@ -7845,11 +8411,11 @@
         </is>
       </c>
       <c r="B11" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A11,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A11,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C11" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A11)-B11</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A11)-B11</f>
         <v/>
       </c>
       <c r="D11" s="57">
@@ -7862,11 +8428,11 @@
         </is>
       </c>
       <c r="G11" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F11,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F11,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H11" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F11)-G11</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F11)-G11</f>
         <v/>
       </c>
       <c r="I11" s="57">
@@ -7881,11 +8447,11 @@
         </is>
       </c>
       <c r="B12" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A12,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A12,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C12" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A12)-B12</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A12)-B12</f>
         <v/>
       </c>
       <c r="D12" s="57">
@@ -7898,11 +8464,11 @@
         </is>
       </c>
       <c r="G12" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F12,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F12,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H12" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F12)-G12</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F12)-G12</f>
         <v/>
       </c>
       <c r="I12" s="57">
@@ -7917,11 +8483,11 @@
         </is>
       </c>
       <c r="B13" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A13,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A13,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C13" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A13)-B13</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A13)-B13</f>
         <v/>
       </c>
       <c r="D13" s="57">
@@ -7934,11 +8500,11 @@
         </is>
       </c>
       <c r="G13" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F13,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F13,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H13" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F13)-G13</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F13)-G13</f>
         <v/>
       </c>
       <c r="I13" s="57">
@@ -7953,11 +8519,11 @@
         </is>
       </c>
       <c r="B14" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A14,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A14,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C14" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A14)-B14</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A14)-B14</f>
         <v/>
       </c>
       <c r="D14" s="57">
@@ -7970,11 +8536,11 @@
         </is>
       </c>
       <c r="G14" s="40">
-        <f>COUNTIFS(準備リスト!$E$5:$E$107,$F14,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F14,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="H14" s="40">
-        <f>COUNTIF(準備リスト!$E$5:$E$107,$F14)-G14</f>
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F14)-G14</f>
         <v/>
       </c>
       <c r="I14" s="57">
@@ -7989,17 +8555,34 @@
         </is>
       </c>
       <c r="B15" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A15,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A15,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C15" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A15)-B15</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A15)-B15</f>
         <v/>
       </c>
       <c r="D15" s="57">
         <f>B15+C15</f>
         <v/>
       </c>
+      <c r="F15" s="58" t="inlineStr">
+        <is>
+          <t>K 体験・展示コーナーの準備</t>
+        </is>
+      </c>
+      <c r="G15" s="40">
+        <f>COUNTIFS(準備リスト!$E$5:$E$119,$F15,準備リスト!$I$5:$I$119,"完了")</f>
+        <v/>
+      </c>
+      <c r="H15" s="40">
+        <f>COUNTIF(準備リスト!$E$5:$E$119,$F15)-G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="57">
+        <f>G15+H15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="39" t="inlineStr">
@@ -8008,34 +8591,17 @@
         </is>
       </c>
       <c r="B16" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A16,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A16,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C16" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A16)-B16</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A16)-B16</f>
         <v/>
       </c>
       <c r="D16" s="57">
         <f>B16+C16</f>
         <v/>
       </c>
-      <c r="F16" s="59" t="inlineStr">
-        <is>
-          <t>全体</t>
-        </is>
-      </c>
-      <c r="G16" s="60">
-        <f>SUM(G5:G14)</f>
-        <v/>
-      </c>
-      <c r="H16" s="30">
-        <f>SUM(H5:H14)</f>
-        <v/>
-      </c>
-      <c r="I16" s="45">
-        <f>SUM(I5:I14)</f>
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="39" t="inlineStr">
@@ -8044,28 +8610,34 @@
         </is>
       </c>
       <c r="B17" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A17,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A17,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C17" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A17)-B17</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A17)-B17</f>
         <v/>
       </c>
       <c r="D17" s="57">
         <f>B17+C17</f>
         <v/>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>進み具合</t>
-        </is>
-      </c>
-      <c r="G17" s="61">
-        <f>IF(I16=0,0,G16/I16)</f>
-        <v/>
-      </c>
-      <c r="H17" s="23" t="n"/>
-      <c r="I17" s="23" t="n"/>
+      <c r="F17" s="59" t="inlineStr">
+        <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="G17" s="60">
+        <f>SUM(G5:G15)</f>
+        <v/>
+      </c>
+      <c r="H17" s="30">
+        <f>SUM(H5:H15)</f>
+        <v/>
+      </c>
+      <c r="I17" s="45">
+        <f>SUM(I5:I15)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="39" t="inlineStr">
@@ -8074,17 +8646,28 @@
         </is>
       </c>
       <c r="B18" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A18,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A18,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C18" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A18)-B18</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A18)-B18</f>
         <v/>
       </c>
       <c r="D18" s="57">
         <f>B18+C18</f>
         <v/>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>進み具合</t>
+        </is>
+      </c>
+      <c r="G18" s="61">
+        <f>IF(I17=0,0,G17/I17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="23" t="n"/>
+      <c r="I18" s="23" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="39" t="inlineStr">
@@ -8093,11 +8676,11 @@
         </is>
       </c>
       <c r="B19" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A19,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A19,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C19" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A19)-B19</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A19)-B19</f>
         <v/>
       </c>
       <c r="D19" s="57">
@@ -8112,11 +8695,11 @@
         </is>
       </c>
       <c r="B20" s="40">
-        <f>COUNTIFS(準備リスト!$D$5:$D$107,$A20,準備リスト!$I$5:$I$107,"完了")</f>
+        <f>COUNTIFS(準備リスト!$D$5:$D$119,$A20,準備リスト!$I$5:$I$119,"完了")</f>
         <v/>
       </c>
       <c r="C20" s="40">
-        <f>COUNTIF(準備リスト!$D$5:$D$107,$A20)-B20</f>
+        <f>COUNTIF(準備リスト!$D$5:$D$119,$A20)-B20</f>
         <v/>
       </c>
       <c r="D20" s="57">

--- a/ボランティアカフェ_開催準備リスト_20261215.xlsx
+++ b/ボランティアカフェ_開催準備リスト_20261215.xlsx
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>粕川地区防災コミュニティセンター</t>
+          <t>粕川地区防災コミュニティーセンター</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
     <row r="2">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>会場：粕川地区防災コミュニティセンター　／　9:00開場　9:30スタート　12:00終了</t>
+          <t>会場：粕川地区防災コミュニティーセンター　／　9:00開場　9:30スタート　12:00終了</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       <c r="J11" s="36" t="n"/>
       <c r="K11" s="37" t="inlineStr">
         <is>
-          <t>10月26日までに役場へ持っていく必要があります</t>
+          <t>10月26日までに役場へ持っていく。予算計上なし（社協内で印刷）</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="G36" s="26" t="inlineStr">
         <is>
-          <t>粕川地区防災コミュニティセンター。前日準備の時間帯に使用申請が要るかも確認</t>
+          <t>粕川地区防災コミュニティーセンター。前日準備の時間帯に使用申請が要るかも確認</t>
         </is>
       </c>
       <c r="H36" s="27" t="n"/>
@@ -3637,7 +3637,7 @@
       <c r="J36" s="36" t="n"/>
       <c r="K36" s="37" t="inlineStr">
         <is>
-          <t>会場は粕川地区防災コミュニティセンターに決定済み</t>
+          <t>会場は粕川地区防災コミュニティーセンターに決定済み</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,11 @@
         </is>
       </c>
       <c r="J45" s="36" t="n"/>
-      <c r="K45" s="37" t="n"/>
+      <c r="K45" s="37" t="inlineStr">
+        <is>
+          <t>予算計上なし。手持ちや借用でまかなう</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="32" t="n">
@@ -7727,7 +7731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7954,16 +7958,16 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>盆栽の道具・汚れ対策</t>
+          <t>印刷</t>
         </is>
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>剪定ばさみ3〜4本、じょうろ、ブルーシート、軍手、雑巾</t>
+          <t>チラシ、講座の配布資料、参加者カード、表示物、各コーナーの説明札</t>
         </is>
       </c>
       <c r="C13" s="49" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="D13" s="49" t="n">
         <v>1</v>
@@ -7974,23 +7978,23 @@
       </c>
       <c r="F13" s="51" t="inlineStr">
         <is>
-          <t>はさみは人数分要りません。回して使います</t>
+          <t>社協内の印刷でまかなうため0円（9/15のご指示）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>印刷</t>
+          <t>消耗品</t>
         </is>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>チラシ、講座の配布資料、参加者カード、表示物、各コーナーの説明札</t>
+          <t>名札、紙コップ、紙皿、おしぼり、ゴミ袋、文具</t>
         </is>
       </c>
       <c r="C14" s="49" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="D14" s="49" t="n">
         <v>1</v>
@@ -7999,25 +8003,21 @@
         <f>C14*D14</f>
         <v/>
       </c>
-      <c r="F14" s="51" t="inlineStr">
-        <is>
-          <t>説明札は模造紙とペンで手書きでも十分です</t>
-        </is>
-      </c>
+      <c r="F14" s="51" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>消耗品</t>
+          <t>講師・協力者へのお礼</t>
         </is>
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>名札、紙コップ、紙皿、おしぼり、ゴミ袋、文具</t>
+          <t>高橋文之さん、防災士、配食ボランティアのみなさんへ</t>
         </is>
       </c>
       <c r="C15" s="49" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="D15" s="49" t="n">
         <v>1</v>
@@ -8026,85 +8026,62 @@
         <f>C15*D15</f>
         <v/>
       </c>
-      <c r="F15" s="51" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>講師・協力者へのお礼</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>高橋文之さん、防災士、配食ボランティアのみなさんへ</t>
-        </is>
-      </c>
-      <c r="C16" s="49" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D16" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="50">
-        <f>C16*D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="51" t="inlineStr">
+      <c r="F15" s="51" t="inlineStr">
         <is>
           <t>品物にするか謝金にするか、規程を確認してください</t>
         </is>
       </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n"/>
+      <c r="B16" s="52" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="53">
+        <f>SUM(E8:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="23" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="23" t="n"/>
       <c r="B17" s="52" t="inlineStr">
         <is>
-          <t>合計</t>
+          <t>予算の残り</t>
         </is>
       </c>
       <c r="C17" s="23" t="n"/>
       <c r="D17" s="23" t="n"/>
-      <c r="E17" s="53">
-        <f>SUM(E8:E16)</f>
-        <v/>
-      </c>
-      <c r="F17" s="23" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n"/>
-      <c r="B18" s="52" t="inlineStr">
-        <is>
-          <t>予算の残り</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="54">
-        <f>$B$4-E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="55" t="inlineStr">
+      <c r="E17" s="54">
+        <f>$B$4-E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="55" t="inlineStr">
         <is>
           <t>マイナスになったら、どこかを削ってください</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>※ 単価・数量はすべて、この表をつくった時点での仮置きです。実際の見積に置き換えてください。総額50,000円は9/2時点で示された額です。参加費は取らないことになったため（9/4）、収入はありません。チラシで定員が50人になったため、茶菓と記念品を55人分で組み直し、単価を下げました。段ボールベッドは町の備蓄から借りる想定で数量0にしています。不足分を買う場合は1台あたり約3,000円かかり、その分は記念品の単価か、盆栽の材料の数を減らして捻出することになります。防災バッグは役場総務課防災対策室からの借用のため、費用は見込んでいません。盆栽の材料は希望者15人分で組んでいます。合計と残りは下の行に自動で出ます。残りがマイナスになったら、どこかを削ってください。</t>
-        </is>
-      </c>
-    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>※ 単価・数量はすべて、この表をつくった時点での仮置きです。実際の見積に置き換えてください。総額50,000円は9/2時点で示された額です。参加費は取らないことになったため（9/4）、収入はありません。チラシで定員が50人になったため、茶菓と記念品を55人分で組み直し、単価を下げました。段ボールベッドは町の備蓄から借りる想定で数量0にしています。不足分を買う場合は1台あたり約3,000円かかり、その分は記念品の単価か、盆栽の材料の数を減らして捻出することになります。防災バッグは役場総務課防災対策室からの借用のため、費用は見込んでいません。盆栽の材料は希望者15人分で組んでいます。盆栽の道具（はさみ・じょうろ・シート等）は手持ちや借用でまかなうため、予算には計上していません（9/15のご指示）。合計と残りは下の行に自動で出ます。残りがマイナスになったら、どこかを削ってください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21"/>
-    <row r="22"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F22"/>
+    <mergeCell ref="A19:F21"/>
   </mergeCells>
-  <conditionalFormatting sqref="E18">
+  <conditionalFormatting sqref="E17">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>$E$18&lt;0</formula>
+      <formula>$E$17&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
